--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Practitioner Role</t>
+    <t>This StructureDefinition contains the maps for VistA NEW PERSON (file 200) to FHIR PractitionerRole</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$69</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2997" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2657" uniqueCount="428">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -246,10 +246,10 @@
     <t>Mapping: FiveWs Pattern Mapping</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t/>
@@ -455,7 +455,116 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>PractitionerRole.extension.id</t>
+    <t>PractitionerRole.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Business Identifiers that are specific to a role/location</t>
+  </si>
+  <si>
+    <t>Business Identifiers that are specific to a role/location.</t>
+  </si>
+  <si>
+    <t>Often, specific identities are assigned for the agent.</t>
+  </si>
+  <si>
+    <t>PRD-7 (or XCN.1)</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>./Identifiers</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>PractitionerRole.active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Whether this practitioner role record is in active use</t>
+  </si>
+  <si>
+    <t>Whether this practitioner role record is in active use.</t>
+  </si>
+  <si>
+    <t>If this value is false, you may refer to the period to see when the role was in active use. If there is no period specified, no inference can be made about when it was active.</t>
+  </si>
+  <si>
+    <t>Need to be able to mark a practitioner role record as not to be used because it was created in error, or otherwise no longer in active use.</t>
+  </si>
+  <si>
+    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+  </si>
+  <si>
+    <t>STF-7</t>
+  </si>
+  <si>
+    <t>.statusCode</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>412: transform using false on NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EXPIRATION DATE (#200-8932.1 &gt; 200.05-3) case date &lt; now</t>
+  </si>
+  <si>
+    <t>StaffSub.ProviderTypeAssignment.ExpirationDate</t>
+  </si>
+  <si>
+    <t>PractitionerRole.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>The period during which the practitioner is authorized to perform in these role(s)</t>
+  </si>
+  <si>
+    <t>The period during which the person is authorized to act as a practitioner in these role(s) for the organization.</t>
+  </si>
+  <si>
+    <t>Even after the agencies is revoked, the fact that it existed must still be recorded.</t>
+  </si>
+  <si>
+    <t>PRD-8/9 / PRA-5.4</t>
+  </si>
+  <si>
+    <t>.performance[@typeCode &lt;= 'PPRF'].ActDefinitionOrEvent.effectiveTime</t>
+  </si>
+  <si>
+    <t>(ServD maps Practitioners and Organizations via another entity, so this concept is not available)</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.period.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -474,7 +583,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>PractitionerRole.extension.extension</t>
+    <t>PractitionerRole.period.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -493,66 +602,152 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>PractitionerRole.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension.value[x]</t>
+    <t>PractitionerRole.period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per-1
+</t>
+  </si>
+  <si>
+    <t>DR.1</t>
+  </si>
+  <si>
+    <t>./low</t>
+  </si>
+  <si>
+    <t>413: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EFFECTIVE DATE (#200-8932.1 &gt; 200.05-2)</t>
+  </si>
+  <si>
+    <t>StaffSub.ProviderTypeAssignment.EffectiveDate</t>
+  </si>
+  <si>
+    <t>PractitionerRole.period.end</t>
+  </si>
+  <si>
+    <t>End time with inclusive boundary, if not ongoing</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+  </si>
+  <si>
+    <t>If the end of the period is missing, it means that the period is ongoing</t>
+  </si>
+  <si>
+    <t>Period.end</t>
+  </si>
+  <si>
+    <t>DR.2</t>
+  </si>
+  <si>
+    <t>./high</t>
+  </si>
+  <si>
+    <t>416: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EXPIRATION DATE (#200-8932.1 &gt; 200.05-3)</t>
+  </si>
+  <si>
+    <t>PractitionerRole.practitioner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner)
+</t>
+  </si>
+  <si>
+    <t>Practitioner that is able to provide the defined services for the organization</t>
+  </si>
+  <si>
+    <t>Practitioner that is able to provide the defined services for the organization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">us-core-13
+</t>
+  </si>
+  <si>
+    <t>.player</t>
+  </si>
+  <si>
+    <t>414: reference from NEW PERSON - NAME (#200-.01)</t>
+  </si>
+  <si>
+    <t>SStaff.PrescribingProvider.StaffName
+SStaff.SStaff.StaffName</t>
+  </si>
+  <si>
+    <t>PractitionerRole.organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization)
+</t>
+  </si>
+  <si>
+    <t>Organization where the roles are available</t>
+  </si>
+  <si>
+    <t>The organization where the Practitioner performs the roles associated.</t>
+  </si>
+  <si>
+    <t>.scoper</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension.value[x]:valueCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension.value[x].coding</t>
+    <t>Roles which this practitioner may perform</t>
+  </si>
+  <si>
+    <t>Roles which this practitioner is authorized to perform for the organization.</t>
+  </si>
+  <si>
+    <t>A person may have more than one role.</t>
+  </si>
+  <si>
+    <t>Need to know what authority the practitioner has - what can they do?</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Provider role codes consisting of NUCC Health Care Provider Taxonomy Code Set for providers.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-provider-role</t>
+  </si>
+  <si>
+    <t>PRD-1 / STF-18  / PRA-3  / PRT-4  / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
@@ -580,10 +775,127 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>PractitionerRole.extension.value[x]:valueCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension.value[x].text</t>
+    <t>PractitionerRole.code.coding.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>1408: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Person Class &gt; PERSON CLASS - X12 CODE (#200-8932.1 &gt; 200.05-.01 &gt; 8932.1-6)</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.text</t>
   </si>
   <si>
     <t>Plain text representation of the concept</t>
@@ -607,395 +919,6 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
-    <t>SStaff.SStaff.PositionTitle
-Staff.Staff.PositionTitle</t>
-  </si>
-  <si>
-    <t>418: source value from NEW PERSON - TITLE &gt; TITLE – NAME (#200-8 &gt; 3.1-.01)</t>
-  </si>
-  <si>
-    <t>PractitionerRole.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Business Identifiers that are specific to a role/location</t>
-  </si>
-  <si>
-    <t>Business Identifiers that are specific to a role/location.</t>
-  </si>
-  <si>
-    <t>Often, specific identities are assigned for the agent.</t>
-  </si>
-  <si>
-    <t>PRD-7 (or XCN.1)</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>./Identifiers</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>PractitionerRole.active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>Whether this practitioner role record is in active use</t>
-  </si>
-  <si>
-    <t>Whether this practitioner role record is in active use.</t>
-  </si>
-  <si>
-    <t>If this value is false, you may refer to the period to see when the role was in active use. If there is no period specified, no inference can be made about when it was active.</t>
-  </si>
-  <si>
-    <t>Need to be able to mark a practitioner role record as not to be used because it was created in error, or otherwise no longer in active use.</t>
-  </si>
-  <si>
-    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
-  </si>
-  <si>
-    <t>STF-7</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>StaffSub.ProviderTypeAssignment.ExpirationDate</t>
-  </si>
-  <si>
-    <t>412: transform using false on NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EXPIRATION DATE (#200-8932.1 &gt; 200.05-3) case date &lt; now</t>
-  </si>
-  <si>
-    <t>PractitionerRole.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>The period during which the practitioner is authorized to perform in these role(s)</t>
-  </si>
-  <si>
-    <t>The period during which the person is authorized to act as a practitioner in these role(s) for the organization.</t>
-  </si>
-  <si>
-    <t>Even after the agencies is revoked, the fact that it existed must still be recorded.</t>
-  </si>
-  <si>
-    <t>PRD-8/9 / PRA-5.4</t>
-  </si>
-  <si>
-    <t>.performance[@typeCode &lt;= 'PPRF'].ActDefinitionOrEvent.effectiveTime</t>
-  </si>
-  <si>
-    <t>(ServD maps Practitioners and Organizations via another entity, so this concept is not available)</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.period.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.period.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.period.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Starting time with inclusive boundary</t>
-  </si>
-  <si>
-    <t>The start of the period. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
-  </si>
-  <si>
-    <t>Period.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per-1
-</t>
-  </si>
-  <si>
-    <t>DR.1</t>
-  </si>
-  <si>
-    <t>./low</t>
-  </si>
-  <si>
-    <t>StaffSub.ProviderTypeAssignment.EffectiveDate</t>
-  </si>
-  <si>
-    <t>413: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EFFECTIVE DATE (#200-8932.1 &gt; 200.05-2)</t>
-  </si>
-  <si>
-    <t>PractitionerRole.period.end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
-  </si>
-  <si>
-    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
-  </si>
-  <si>
-    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
-  </si>
-  <si>
-    <t>If the end of the period is missing, it means that the period is ongoing</t>
-  </si>
-  <si>
-    <t>Period.end</t>
-  </si>
-  <si>
-    <t>DR.2</t>
-  </si>
-  <si>
-    <t>./high</t>
-  </si>
-  <si>
-    <t>416: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EXPIRATION DATE (#200-8932.1 &gt; 200.05-3)</t>
-  </si>
-  <si>
-    <t>PractitionerRole.practitioner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner)
-</t>
-  </si>
-  <si>
-    <t>Practitioner that is able to provide the defined services for the organization</t>
-  </si>
-  <si>
-    <t>Practitioner that is able to provide the defined services for the organization.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">us-core-13
-</t>
-  </si>
-  <si>
-    <t>.player</t>
-  </si>
-  <si>
-    <t>SStaff.PrescribingProvider.StaffName
-SStaff.SStaff.StaffName</t>
-  </si>
-  <si>
-    <t>414: reference from NEW PERSON - NAME (#200-.01)</t>
-  </si>
-  <si>
-    <t>PractitionerRole.organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization)
-</t>
-  </si>
-  <si>
-    <t>Organization where the roles are available</t>
-  </si>
-  <si>
-    <t>The organization where the Practitioner performs the roles associated.</t>
-  </si>
-  <si>
-    <t>.scoper</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code</t>
-  </si>
-  <si>
-    <t>Roles which this practitioner may perform</t>
-  </si>
-  <si>
-    <t>Roles which this practitioner is authorized to perform for the organization.</t>
-  </si>
-  <si>
-    <t>A person may have more than one role.</t>
-  </si>
-  <si>
-    <t>Need to know what authority the practitioner has - what can they do?</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Provider role codes consisting of NUCC Health Care Provider Taxonomy Code Set for providers.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-provider-role</t>
-  </si>
-  <si>
-    <t>PRD-1 / STF-18  / PRA-3  / PRT-4  / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.coding</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.coding.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.coding.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>1408: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Person Class &gt; PERSON CLASS - X12 CODE (#200-8932.1 &gt; 200.05-.01 &gt; 8932.1-6)</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.text</t>
-  </si>
-  <si>
     <t>PractitionerRole.specialty</t>
   </si>
   <si>
@@ -1041,10 +964,10 @@
     <t>PractitionerRole.specialty.coding.code</t>
   </si>
   <si>
+    <t>419: source value from PERSON CLASS - X12 CODE (#8932.1-6)</t>
+  </si>
+  <si>
     <t>Dim.ProviderType.X12Code</t>
-  </si>
-  <si>
-    <t>419: source value from PERSON CLASS - X12 CODE (#8932.1-6)</t>
   </si>
   <si>
     <t>PractitionerRole.specialty.coding.display</t>
@@ -1190,11 +1113,11 @@
     <t>./Value</t>
   </si>
   <si>
+    <t>391: source value from NEW PERSON - EMAIL ADDRESS (#200-.151)</t>
+  </si>
+  <si>
     <t>SStaff.PrescribingProvider.EmailAddress
 SStaff.SStaff.EmailAddress</t>
-  </si>
-  <si>
-    <t>391: source value from NEW PERSON - EMAIL ADDRESS (#200-.151)</t>
   </si>
   <si>
     <t>PractitionerRole.telecom.use</t>
@@ -1735,12 +1658,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP78"/>
+  <dimension ref="A1:AP69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="64.7265625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.96875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.96875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1777,8 +1700,8 @@
     <col min="38" max="38" width="78.58203125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="194.47265625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="46.59375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="148.234375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="148.234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="46.59375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2876,35 +2799,39 @@
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>78</v>
       </c>
@@ -2958,19 +2885,19 @@
         <v>79</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>78</v>
@@ -2987,14 +2914,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3010,21 +2937,21 @@
         <v>78</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O11" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>78</v>
       </c>
@@ -3060,19 +2987,19 @@
         <v>78</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3084,19 +3011,19 @@
         <v>78</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>78</v>
@@ -3107,10 +3034,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3118,7 +3045,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>89</v>
@@ -3130,72 +3057,76 @@
         <v>78</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="P12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="R12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="N12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O12" s="2"/>
-      <c r="P12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>157</v>
-      </c>
       <c r="AG12" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
         <v>89</v>
@@ -3204,33 +3135,33 @@
         <v>78</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3250,19 +3181,21 @@
         <v>78</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+      <c r="O13" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>78</v>
       </c>
@@ -3298,17 +3231,19 @@
         <v>78</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AC13" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>163</v>
+        <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3323,16 +3258,16 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>78</v>
+        <v>174</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>78</v>
@@ -3343,14 +3278,12 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>78</v>
       </c>
@@ -3371,13 +3304,13 @@
         <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3428,7 +3361,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3440,13 +3373,13 @@
         <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>78</v>
@@ -3463,21 +3396,21 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>78</v>
@@ -3489,15 +3422,17 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
@@ -3534,37 +3469,37 @@
         <v>78</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>78</v>
+        <v>185</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>78</v>
@@ -3581,21 +3516,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>78</v>
@@ -3604,19 +3539,19 @@
         <v>78</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>136</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>138</v>
+        <v>192</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3654,37 +3589,37 @@
         <v>78</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>146</v>
+        <v>196</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
@@ -3693,18 +3628,18 @@
         <v>78</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3715,7 +3650,7 @@
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>78</v>
@@ -3727,24 +3662,24 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q17" s="2"/>
+      <c r="Q17" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="R17" t="s" s="2">
         <v>78</v>
       </c>
@@ -3788,25 +3723,25 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -3815,18 +3750,18 @@
         <v>78</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3840,7 +3775,7 @@
         <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>78</v>
@@ -3849,20 +3784,16 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
       </c>
@@ -3910,7 +3841,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3919,16 +3850,16 @@
         <v>89</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>188</v>
+        <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -3937,54 +3868,50 @@
         <v>78</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>191</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J19" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="J19" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K19" t="s" s="2">
-        <v>135</v>
+        <v>217</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
       </c>
@@ -4032,25 +3959,25 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>132</v>
+        <v>220</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
@@ -4067,10 +3994,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4084,7 +4011,7 @@
         <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>78</v>
@@ -4093,17 +4020,19 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="O20" t="s" s="2">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -4128,13 +4057,13 @@
         <v>78</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>78</v>
+        <v>228</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>78</v>
+        <v>229</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>78</v>
@@ -4152,7 +4081,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4167,16 +4096,16 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>78</v>
@@ -4187,10 +4116,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4210,29 +4139,23 @@
         <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q21" t="s" s="2">
-        <v>212</v>
-      </c>
+      <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
         <v>78</v>
       </c>
@@ -4276,7 +4199,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4288,44 +4211,44 @@
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>217</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>78</v>
@@ -4334,21 +4257,21 @@
         <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>219</v>
+        <v>135</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>220</v>
+        <v>136</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>78</v>
       </c>
@@ -4384,43 +4307,43 @@
         <v>78</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>78</v>
+        <v>185</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>223</v>
+        <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>224</v>
+        <v>181</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>78</v>
@@ -4431,10 +4354,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4445,7 +4368,7 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>78</v>
@@ -4454,19 +4377,23 @@
         <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>142</v>
+        <v>235</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>143</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -4514,25 +4441,25 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>145</v>
+        <v>240</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>146</v>
+        <v>242</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -4549,21 +4476,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>78</v>
@@ -4575,17 +4502,15 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4622,37 +4547,37 @@
         <v>78</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -4669,21 +4594,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
@@ -4692,19 +4617,19 @@
         <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>230</v>
+        <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>231</v>
+        <v>136</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>232</v>
+        <v>183</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>233</v>
+        <v>138</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4742,37 +4667,37 @@
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>78</v>
+        <v>185</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>234</v>
+        <v>187</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>237</v>
+        <v>181</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4781,18 +4706,18 @@
         <v>78</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>239</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4815,24 +4740,24 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>230</v>
+        <v>103</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q26" t="s" s="2">
-        <v>244</v>
-      </c>
+      <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4876,7 +4801,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4885,16 +4810,16 @@
         <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4903,18 +4828,18 @@
         <v>78</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4928,7 +4853,7 @@
         <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>78</v>
@@ -4937,15 +4862,17 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4994,7 +4921,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5003,16 +4930,16 @@
         <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>253</v>
+        <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5021,18 +4948,18 @@
         <v>78</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>255</v>
+        <v>78</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>256</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5046,7 +4973,7 @@
         <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>78</v>
@@ -5055,16 +4982,18 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>258</v>
+        <v>109</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+      <c r="O28" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5112,7 +5041,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5121,16 +5050,16 @@
         <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>253</v>
+        <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5139,7 +5068,7 @@
         <v>78</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>78</v>
@@ -5147,10 +5076,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5161,10 +5090,10 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>78</v>
@@ -5173,19 +5102,17 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -5210,13 +5137,13 @@
         <v>78</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>268</v>
+        <v>78</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>269</v>
+        <v>78</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>78</v>
@@ -5234,13 +5161,13 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>78</v>
@@ -5249,13 +5176,13 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5269,10 +5196,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5292,19 +5219,23 @@
         <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>143</v>
+        <v>276</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
@@ -5352,7 +5283,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>145</v>
+        <v>280</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5364,13 +5295,13 @@
         <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>78</v>
+        <v>281</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>146</v>
+        <v>282</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5387,21 +5318,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>78</v>
@@ -5410,21 +5341,23 @@
         <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>136</v>
+        <v>284</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>148</v>
+        <v>285</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5460,37 +5393,37 @@
         <v>78</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>152</v>
+        <v>288</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>146</v>
+        <v>290</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5507,10 +5440,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5524,7 +5457,7 @@
         <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>78</v>
@@ -5533,20 +5466,16 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>173</v>
+        <v>222</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>174</v>
+        <v>292</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
@@ -5570,13 +5499,11 @@
         <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>78</v>
+        <v>294</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5594,7 +5521,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5609,13 +5536,13 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>179</v>
+        <v>295</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>180</v>
+        <v>296</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>78</v>
+        <v>297</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -5629,10 +5556,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5655,13 +5582,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5712,7 +5639,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5730,7 +5657,7 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -5747,10 +5674,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5779,7 +5706,7 @@
         <v>136</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>138</v>
@@ -5820,19 +5747,19 @@
         <v>78</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5850,7 +5777,7 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -5867,10 +5794,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5881,7 +5808,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>78</v>
@@ -5893,19 +5820,19 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>103</v>
+        <v>235</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>279</v>
+        <v>237</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>280</v>
+        <v>238</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5954,13 +5881,13 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>282</v>
+        <v>240</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>78</v>
@@ -5969,10 +5896,10 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>283</v>
+        <v>241</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>284</v>
+        <v>242</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -5989,10 +5916,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6012,20 +5939,18 @@
         <v>78</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>286</v>
+        <v>178</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6074,7 +5999,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>289</v>
+        <v>180</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6086,13 +6011,13 @@
         <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>290</v>
+        <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>291</v>
+        <v>181</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6109,21 +6034,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
@@ -6132,21 +6057,21 @@
         <v>78</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>293</v>
+        <v>136</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6182,37 +6107,37 @@
         <v>78</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>78</v>
+        <v>185</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>296</v>
+        <v>187</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>298</v>
+        <v>181</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6224,15 +6149,15 @@
         <v>78</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>299</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6255,17 +6180,19 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>301</v>
+        <v>246</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O38" t="s" s="2">
-        <v>303</v>
+        <v>249</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6314,7 +6241,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>304</v>
+        <v>250</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6329,10 +6256,10 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>305</v>
+        <v>251</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6349,10 +6276,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6375,20 +6302,18 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>308</v>
+        <v>254</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>309</v>
+        <v>255</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
       </c>
@@ -6436,7 +6361,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>312</v>
+        <v>257</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6451,10 +6376,10 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>313</v>
+        <v>258</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>314</v>
+        <v>259</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6471,10 +6396,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6497,19 +6422,17 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>183</v>
+        <v>261</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>186</v>
+        <v>263</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -6558,7 +6481,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6573,10 +6496,10 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>188</v>
+        <v>265</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>189</v>
+        <v>266</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6585,18 +6508,18 @@
         <v>78</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>78</v>
+        <v>306</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6607,10 +6530,10 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>78</v>
@@ -6619,16 +6542,18 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>317</v>
+        <v>269</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>318</v>
+        <v>270</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
@@ -6652,11 +6577,13 @@
         <v>78</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z41" t="s" s="2">
-        <v>319</v>
+        <v>78</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>78</v>
@@ -6674,13 +6601,13 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>316</v>
+        <v>272</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>78</v>
@@ -6689,13 +6616,13 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>320</v>
+        <v>273</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>321</v>
+        <v>274</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>322</v>
+        <v>78</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>78</v>
@@ -6709,10 +6636,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6732,19 +6659,23 @@
         <v>78</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>143</v>
+        <v>276</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6792,7 +6723,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>145</v>
+        <v>280</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6804,13 +6735,13 @@
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>78</v>
+        <v>281</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>146</v>
+        <v>282</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6827,21 +6758,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -6850,21 +6781,23 @@
         <v>78</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>136</v>
+        <v>284</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>148</v>
+        <v>285</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6900,37 +6833,37 @@
         <v>78</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>152</v>
+        <v>288</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>146</v>
+        <v>290</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6947,10 +6880,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6964,7 +6897,7 @@
         <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>78</v>
@@ -6973,20 +6906,16 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>173</v>
+        <v>312</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>174</v>
+        <v>313</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
@@ -7034,7 +6963,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>178</v>
+        <v>311</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7043,25 +6972,25 @@
         <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>180</v>
+        <v>315</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>78</v>
+        <v>316</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>78</v>
+        <v>317</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>78</v>
+        <v>318</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>78</v>
@@ -7069,10 +6998,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7083,7 +7012,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>78</v>
@@ -7095,13 +7024,13 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>142</v>
+        <v>320</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>143</v>
+        <v>321</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>144</v>
+        <v>322</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7152,25 +7081,25 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>145</v>
+        <v>319</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>78</v>
+        <v>323</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>146</v>
+        <v>324</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7187,14 +7116,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7204,27 +7133,27 @@
         <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>135</v>
+        <v>326</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>136</v>
+        <v>327</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7260,19 +7189,19 @@
         <v>78</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>152</v>
+        <v>325</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7281,16 +7210,16 @@
         <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>78</v>
+        <v>330</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>146</v>
+        <v>331</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7307,10 +7236,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7330,23 +7259,19 @@
         <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>103</v>
+        <v>177</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>278</v>
+        <v>178</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7394,7 +7319,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>282</v>
+        <v>180</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7406,13 +7331,13 @@
         <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>283</v>
+        <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>284</v>
+        <v>181</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7429,21 +7354,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>78</v>
@@ -7452,19 +7377,19 @@
         <v>78</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>286</v>
+        <v>136</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>287</v>
+        <v>183</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>288</v>
+        <v>138</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7502,37 +7427,37 @@
         <v>78</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>78</v>
+        <v>185</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>289</v>
+        <v>187</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>290</v>
+        <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>291</v>
+        <v>181</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7549,10 +7474,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7560,13 +7485,13 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>78</v>
@@ -7578,15 +7503,13 @@
         <v>109</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>293</v>
+        <v>335</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>294</v>
+        <v>336</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>295</v>
-      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7610,13 +7533,13 @@
         <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>78</v>
+        <v>338</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7634,7 +7557,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>296</v>
+        <v>340</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7643,36 +7566,36 @@
         <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>78</v>
+        <v>341</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>297</v>
+        <v>342</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>298</v>
+        <v>343</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>331</v>
+        <v>78</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7680,13 +7603,13 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>78</v>
@@ -7695,17 +7618,19 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>301</v>
+        <v>346</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>303</v>
+        <v>349</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7754,7 +7679,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7769,30 +7694,30 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>305</v>
+        <v>351</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>78</v>
+        <v>353</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>78</v>
+        <v>354</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>78</v>
+        <v>355</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7809,25 +7734,25 @@
         <v>78</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>207</v>
+        <v>109</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>308</v>
+        <v>357</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>309</v>
+        <v>358</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>310</v>
+        <v>359</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -7852,13 +7777,13 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>78</v>
+        <v>361</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>78</v>
+        <v>362</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -7876,7 +7801,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>312</v>
+        <v>363</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7891,13 +7816,13 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>314</v>
+        <v>365</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>78</v>
+        <v>366</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -7911,10 +7836,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7937,20 +7862,18 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>142</v>
+        <v>368</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>183</v>
+        <v>369</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>184</v>
+        <v>370</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7998,7 +7921,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>187</v>
+        <v>372</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8013,10 +7936,10 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
@@ -8033,10 +7956,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8047,10 +7970,10 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>78</v>
@@ -8059,13 +7982,13 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>337</v>
+        <v>168</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>338</v>
+        <v>374</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>339</v>
+        <v>375</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8116,45 +8039,45 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>336</v>
+        <v>376</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>253</v>
+        <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>341</v>
+        <v>378</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>342</v>
+        <v>78</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>343</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>344</v>
+        <v>379</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>344</v>
+        <v>379</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8177,15 +8100,17 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>345</v>
+        <v>380</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>346</v>
+        <v>381</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8234,7 +8159,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>344</v>
+        <v>379</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8243,16 +8168,16 @@
         <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>253</v>
+        <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>348</v>
+        <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8269,10 +8194,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8283,30 +8208,28 @@
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>351</v>
+        <v>177</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>352</v>
+        <v>178</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>353</v>
+        <v>179</v>
       </c>
       <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>354</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8354,25 +8277,25 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>355</v>
+        <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>356</v>
+        <v>181</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8389,21 +8312,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>357</v>
+        <v>386</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>357</v>
+        <v>386</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
@@ -8415,15 +8338,17 @@
         <v>78</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8472,25 +8397,25 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8507,14 +8432,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>134</v>
+        <v>388</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8527,24 +8452,26 @@
         <v>78</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>136</v>
+        <v>389</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>148</v>
+        <v>390</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="O57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8580,19 +8507,19 @@
         <v>78</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>152</v>
+        <v>391</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8610,7 +8537,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8627,10 +8554,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8638,28 +8565,28 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>360</v>
+        <v>393</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>361</v>
+        <v>394</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8686,13 +8613,13 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>362</v>
+        <v>337</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -8710,28 +8637,28 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>366</v>
+        <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>367</v>
+        <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>369</v>
+        <v>78</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8745,10 +8672,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8756,35 +8683,31 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
@@ -8832,7 +8755,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8847,30 +8770,30 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>376</v>
+        <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>378</v>
+        <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>379</v>
+        <v>78</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>380</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8887,26 +8810,24 @@
         <v>78</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>109</v>
+        <v>401</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -8930,13 +8851,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>362</v>
+        <v>78</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>387</v>
+        <v>78</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -8954,7 +8875,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8969,13 +8890,13 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>391</v>
+        <v>78</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8989,10 +8910,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9012,19 +8933,19 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9074,7 +8995,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9089,10 +9010,10 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>146</v>
+        <v>384</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9109,10 +9030,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9123,7 +9044,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9132,16 +9053,16 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>219</v>
+        <v>380</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9192,13 +9113,13 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
@@ -9207,13 +9128,13 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9227,10 +9148,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9241,7 +9162,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -9253,17 +9174,15 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>405</v>
+        <v>177</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>406</v>
+        <v>178</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9312,25 +9231,25 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>404</v>
+        <v>180</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>409</v>
+        <v>181</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9347,21 +9266,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>78</v>
@@ -9373,15 +9292,17 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9430,25 +9351,25 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -9465,14 +9386,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>134</v>
+        <v>388</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9485,24 +9406,26 @@
         <v>78</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>136</v>
+        <v>389</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>148</v>
+        <v>390</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="O65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9550,7 +9473,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>152</v>
+        <v>391</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9568,7 +9491,7 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
@@ -9585,46 +9508,42 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>413</v>
+        <v>78</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9672,25 +9591,25 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9721,7 +9640,7 @@
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>78</v>
@@ -9733,7 +9652,7 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>109</v>
+        <v>168</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>418</v>
@@ -9766,13 +9685,13 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>362</v>
+        <v>78</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>421</v>
+        <v>78</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -9796,7 +9715,7 @@
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>78</v>
@@ -9808,7 +9727,7 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9825,10 +9744,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9851,13 +9770,13 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9908,7 +9827,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9926,7 +9845,7 @@
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
@@ -9943,10 +9862,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9957,10 +9876,10 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>78</v>
@@ -9969,18 +9888,18 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -10028,16 +9947,16 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>78</v>
+        <v>330</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>101</v>
@@ -10046,7 +9965,7 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>409</v>
+        <v>181</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -10058,1083 +9977,11 @@
         <v>78</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="P78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP78" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP78">
+  <autoFilter ref="A1:AP69">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11144,7 +9991,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI77">
+  <conditionalFormatting sqref="A2:AI68">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$78</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2657" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2995" uniqueCount="465">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -431,28 +431,225 @@
     <t>PractitionerRole.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:practitioner-job-title</t>
+  </si>
+  <si>
+    <t>practitioner-job-title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {practitioner-job-title}
+</t>
+  </si>
+  <si>
+    <t>Job Title</t>
+  </si>
+  <si>
+    <t>The Job Title for this practitioner/practitionerrole</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:practitioner-job-title.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:practitioner-job-title.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:practitioner-job-title.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/practitioner-job-title</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:practitioner-job-title.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Job title</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/practitioner-job-title</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:practitioner-job-title.value[x].id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension.value[x].id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:practitioner-job-title.value[x].extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension.value[x].extension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:practitioner-job-title.value[x].coding</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension.value[x].coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:practitioner-job-title.value[x].text</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension.value[x].text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>418: source value from NEW PERSON - TITLE &gt; TITLE – NAME (#200-8 &gt; 3.1-.01)</t>
+  </si>
+  <si>
+    <t>SStaff.SStaff.PositionTitle
+Staff.Staff.PositionTitle</t>
   </si>
   <si>
     <t>PractitionerRole.modifierExtension</t>
@@ -567,39 +764,7 @@
     <t>PractitionerRole.period.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>PractitionerRole.period.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>PractitionerRole.period.start</t>
@@ -710,10 +875,6 @@
     <t>PractitionerRole.code</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>Roles which this practitioner may perform</t>
   </si>
   <si>
@@ -750,31 +911,6 @@
     <t>PractitionerRole.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
     <t>PractitionerRole.code.coding.id</t>
   </si>
   <si>
@@ -896,27 +1032,6 @@
   </si>
   <si>
     <t>PractitionerRole.code.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>PractitionerRole.specialty</t>
@@ -1658,12 +1773,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP69"/>
+  <dimension ref="A1:AP78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.96875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="61.890625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.96875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="19.41796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2679,7 +2794,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2698,17 +2813,15 @@
         <v>78</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>138</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>78</v>
@@ -2745,16 +2858,14 @@
         <v>78</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>139</v>
@@ -2775,7 +2886,7 @@
         <v>78</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>78</v>
@@ -2795,43 +2906,41 @@
         <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>78</v>
       </c>
@@ -2879,7 +2988,7 @@
         <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2897,7 +3006,7 @@
         <v>78</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>78</v>
@@ -2917,7 +3026,7 @@
         <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2928,7 +3037,7 @@
         <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>78</v>
@@ -2937,10 +3046,10 @@
         <v>78</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>148</v>
@@ -2949,9 +3058,7 @@
         <v>149</v>
       </c>
       <c r="N11" s="2"/>
-      <c r="O11" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>78</v>
       </c>
@@ -2999,31 +3106,31 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>152</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>78</v>
@@ -3034,10 +3141,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3048,7 +3155,7 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>78</v>
@@ -3057,111 +3164,105 @@
         <v>78</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="P12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="R12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>155</v>
-      </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>163</v>
+        <v>78</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3169,7 +3270,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>89</v>
@@ -3181,27 +3282,27 @@
         <v>78</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>168</v>
+        <v>103</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>78</v>
@@ -3243,10 +3344,10 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>89</v>
@@ -3255,19 +3356,19 @@
         <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>172</v>
+        <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>78</v>
@@ -3278,10 +3379,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3289,7 +3390,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>89</v>
@@ -3304,13 +3405,13 @@
         <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3337,13 +3438,13 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>78</v>
+        <v>169</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -3361,7 +3462,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3370,16 +3471,16 @@
         <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>78</v>
@@ -3396,21 +3497,21 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>78</v>
@@ -3422,17 +3523,15 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
@@ -3469,37 +3568,37 @@
         <v>78</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>78</v>
@@ -3516,21 +3615,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>78</v>
@@ -3539,19 +3638,19 @@
         <v>78</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3589,37 +3688,37 @@
         <v>78</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>156</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>196</v>
+        <v>152</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
@@ -3628,18 +3727,18 @@
         <v>78</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3650,7 +3749,7 @@
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>78</v>
@@ -3662,24 +3761,24 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="O17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L17" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q17" t="s" s="2">
-        <v>203</v>
-      </c>
+      <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
         <v>78</v>
       </c>
@@ -3723,25 +3822,25 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -3750,18 +3849,18 @@
         <v>78</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3775,7 +3874,7 @@
         <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>78</v>
@@ -3784,16 +3883,20 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>78</v>
       </c>
@@ -3841,7 +3944,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3850,16 +3953,16 @@
         <v>89</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -3868,50 +3971,54 @@
         <v>78</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>215</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I19" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I19" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>217</v>
+        <v>134</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>78</v>
       </c>
@@ -3959,25 +4066,25 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>220</v>
+        <v>132</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
@@ -3994,10 +4101,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4011,7 +4118,7 @@
         <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>78</v>
@@ -4020,19 +4127,17 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -4057,13 +4162,13 @@
         <v>78</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>229</v>
+        <v>78</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>78</v>
@@ -4081,7 +4186,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4096,16 +4201,16 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>78</v>
+        <v>217</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>78</v>
@@ -4116,10 +4221,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4139,23 +4244,29 @@
         <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q21" s="2"/>
+      <c r="Q21" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="R21" t="s" s="2">
         <v>78</v>
       </c>
@@ -4199,7 +4310,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4211,44 +4322,44 @@
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>78</v>
+        <v>225</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>78</v>
+        <v>228</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>78</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>78</v>
@@ -4257,21 +4368,21 @@
         <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>135</v>
+        <v>231</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>136</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
       </c>
@@ -4307,43 +4418,43 @@
         <v>78</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>187</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>78</v>
+        <v>235</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>181</v>
+        <v>236</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>78</v>
@@ -4354,10 +4465,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4368,7 +4479,7 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>78</v>
@@ -4377,23 +4488,19 @@
         <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>235</v>
+        <v>176</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>236</v>
+        <v>148</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -4441,25 +4548,25 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>241</v>
+        <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>242</v>
+        <v>152</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -4476,21 +4583,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>78</v>
@@ -4502,15 +4609,17 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4547,37 +4656,37 @@
         <v>78</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -4594,21 +4703,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
@@ -4617,19 +4726,19 @@
         <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>135</v>
+        <v>242</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>136</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>183</v>
+        <v>244</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>138</v>
+        <v>245</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4667,37 +4776,37 @@
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>187</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>78</v>
+        <v>247</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4706,18 +4815,18 @@
         <v>78</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>78</v>
+        <v>250</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>78</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4740,24 +4849,24 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>103</v>
+        <v>242</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q26" s="2"/>
+      <c r="Q26" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="R26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4801,7 +4910,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4810,16 +4919,16 @@
         <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>247</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4828,18 +4937,18 @@
         <v>78</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>78</v>
+        <v>260</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>78</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4853,7 +4962,7 @@
         <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>78</v>
@@ -4862,17 +4971,15 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>177</v>
+        <v>262</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4921,7 +5028,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4930,16 +5037,16 @@
         <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -4948,18 +5055,18 @@
         <v>78</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>78</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4973,7 +5080,7 @@
         <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>78</v>
@@ -4982,18 +5089,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>109</v>
+        <v>270</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="N28" s="2"/>
-      <c r="O28" t="s" s="2">
-        <v>263</v>
-      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5041,7 +5146,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5050,16 +5155,16 @@
         <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>265</v>
+        <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5068,7 +5173,7 @@
         <v>78</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>78</v>
@@ -5076,10 +5181,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5090,10 +5195,10 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>78</v>
@@ -5102,17 +5207,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="O29" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -5137,13 +5244,13 @@
         <v>78</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>78</v>
+        <v>279</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>78</v>
+        <v>280</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>78</v>
+        <v>281</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>78</v>
@@ -5161,13 +5268,13 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>78</v>
@@ -5176,13 +5283,13 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5196,10 +5303,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5219,23 +5326,19 @@
         <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>148</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
@@ -5283,7 +5386,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>280</v>
+        <v>150</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5295,13 +5398,13 @@
         <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>281</v>
+        <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>282</v>
+        <v>152</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5318,21 +5421,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>78</v>
@@ -5341,23 +5444,21 @@
         <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>284</v>
+        <v>180</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
+        <v>181</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5393,37 +5494,37 @@
         <v>78</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>288</v>
+        <v>156</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>290</v>
+        <v>152</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5440,10 +5541,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5457,7 +5558,7 @@
         <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>78</v>
@@ -5466,16 +5567,20 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>292</v>
+        <v>186</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
@@ -5499,11 +5604,13 @@
         <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>294</v>
+        <v>78</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5521,7 +5628,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>291</v>
+        <v>190</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5536,13 +5643,13 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>295</v>
+        <v>191</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>296</v>
+        <v>192</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -5556,10 +5663,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5582,13 +5689,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5639,7 +5746,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5657,7 +5764,7 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -5674,14 +5781,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5700,16 +5807,16 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5747,19 +5854,19 @@
         <v>78</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>184</v>
+        <v>137</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>186</v>
+        <v>138</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5777,7 +5884,7 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -5794,10 +5901,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5808,7 +5915,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>78</v>
@@ -5820,19 +5927,19 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>235</v>
+        <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>236</v>
+        <v>290</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>237</v>
+        <v>291</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>238</v>
+        <v>292</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>239</v>
+        <v>293</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5881,13 +5988,13 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>240</v>
+        <v>294</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>78</v>
@@ -5896,10 +6003,10 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>241</v>
+        <v>295</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>242</v>
+        <v>296</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -5916,10 +6023,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5939,18 +6046,20 @@
         <v>78</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>178</v>
+        <v>298</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5999,7 +6108,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>180</v>
+        <v>301</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6011,13 +6120,13 @@
         <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>78</v>
+        <v>302</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>181</v>
+        <v>303</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6034,21 +6143,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
@@ -6057,21 +6166,21 @@
         <v>78</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>136</v>
+        <v>305</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6107,37 +6216,37 @@
         <v>78</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>187</v>
+        <v>308</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>78</v>
+        <v>309</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>181</v>
+        <v>310</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6146,7 +6255,7 @@
         <v>78</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>78</v>
+        <v>311</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>78</v>
@@ -6154,10 +6263,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6180,19 +6289,17 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>246</v>
+        <v>313</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>249</v>
+        <v>315</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6241,7 +6348,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>250</v>
+        <v>316</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6256,10 +6363,10 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>251</v>
+        <v>317</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>252</v>
+        <v>318</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6276,10 +6383,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6302,18 +6409,20 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>254</v>
+        <v>320</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>255</v>
+        <v>321</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
       </c>
@@ -6361,7 +6470,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>257</v>
+        <v>324</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6376,10 +6485,10 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>258</v>
+        <v>325</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6396,10 +6505,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6422,17 +6531,19 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>109</v>
+        <v>176</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>261</v>
+        <v>195</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>263</v>
+        <v>198</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -6481,7 +6592,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>264</v>
+        <v>199</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6496,10 +6607,10 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>265</v>
+        <v>200</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>266</v>
+        <v>201</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6508,18 +6619,18 @@
         <v>78</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>306</v>
+        <v>78</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>307</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6530,10 +6641,10 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>78</v>
@@ -6542,18 +6653,16 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>269</v>
+        <v>329</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>271</v>
-      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
@@ -6577,13 +6686,11 @@
         <v>78</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>78</v>
+        <v>331</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>78</v>
@@ -6601,13 +6708,13 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>272</v>
+        <v>328</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>78</v>
@@ -6616,13 +6723,13 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>273</v>
+        <v>332</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>274</v>
+        <v>333</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>78</v>
+        <v>334</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>78</v>
@@ -6636,10 +6743,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6659,23 +6766,19 @@
         <v>78</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>276</v>
+        <v>148</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6723,7 +6826,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>280</v>
+        <v>150</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6735,13 +6838,13 @@
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>281</v>
+        <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>282</v>
+        <v>152</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6758,21 +6861,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -6781,23 +6884,21 @@
         <v>78</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>284</v>
+        <v>180</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>285</v>
+        <v>181</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6833,37 +6934,37 @@
         <v>78</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>288</v>
+        <v>156</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>290</v>
+        <v>152</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6880,10 +6981,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6897,7 +6998,7 @@
         <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>78</v>
@@ -6906,16 +7007,20 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>312</v>
+        <v>185</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>313</v>
+        <v>186</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
@@ -6963,7 +7068,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>311</v>
+        <v>190</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6972,25 +7077,25 @@
         <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>315</v>
+        <v>192</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>316</v>
+        <v>78</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>317</v>
+        <v>78</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>318</v>
+        <v>78</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>78</v>
@@ -6998,10 +7103,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7012,7 +7117,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>78</v>
@@ -7024,13 +7129,13 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>320</v>
+        <v>176</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>321</v>
+        <v>148</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>322</v>
+        <v>149</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7081,25 +7186,25 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>319</v>
+        <v>150</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>323</v>
+        <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>324</v>
+        <v>152</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7116,14 +7221,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7133,27 +7238,27 @@
         <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>326</v>
+        <v>134</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>327</v>
+        <v>180</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7189,19 +7294,19 @@
         <v>78</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>325</v>
+        <v>156</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7210,16 +7315,16 @@
         <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>330</v>
+        <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>331</v>
+        <v>152</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7236,10 +7341,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7259,19 +7364,23 @@
         <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>177</v>
+        <v>103</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>178</v>
+        <v>290</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7319,7 +7428,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>180</v>
+        <v>294</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7331,13 +7440,13 @@
         <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>78</v>
+        <v>295</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>181</v>
+        <v>296</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7354,21 +7463,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>78</v>
@@ -7377,19 +7486,19 @@
         <v>78</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>136</v>
+        <v>298</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>183</v>
+        <v>299</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7427,37 +7536,37 @@
         <v>78</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>187</v>
+        <v>301</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>78</v>
+        <v>302</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>181</v>
+        <v>303</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7474,10 +7583,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7485,13 +7594,13 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>78</v>
@@ -7503,13 +7612,15 @@
         <v>109</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>335</v>
+        <v>305</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>336</v>
+        <v>306</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7533,13 +7644,13 @@
         <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>337</v>
+        <v>78</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>338</v>
+        <v>78</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7557,7 +7668,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>340</v>
+        <v>308</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7566,28 +7677,28 @@
         <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>341</v>
+        <v>78</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>342</v>
+        <v>309</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -7603,13 +7714,13 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>78</v>
@@ -7618,19 +7729,17 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>349</v>
+        <v>315</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7679,7 +7788,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>350</v>
+        <v>316</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7694,30 +7803,30 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>353</v>
+        <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>354</v>
+        <v>78</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>355</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7734,25 +7843,25 @@
         <v>78</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>109</v>
+        <v>219</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>357</v>
+        <v>320</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>358</v>
+        <v>321</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>359</v>
+        <v>322</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>360</v>
+        <v>323</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -7777,13 +7886,13 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>337</v>
+        <v>78</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>361</v>
+        <v>78</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>362</v>
+        <v>78</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -7801,7 +7910,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>363</v>
+        <v>324</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7816,13 +7925,13 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>364</v>
+        <v>325</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>365</v>
+        <v>326</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>366</v>
+        <v>78</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -7836,10 +7945,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7862,18 +7971,20 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>368</v>
+        <v>176</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>369</v>
+        <v>195</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>370</v>
+        <v>196</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7921,7 +8032,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>372</v>
+        <v>199</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7936,10 +8047,10 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
@@ -7956,10 +8067,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7970,10 +8081,10 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>78</v>
@@ -7982,13 +8093,13 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>168</v>
+        <v>349</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8039,34 +8150,34 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>376</v>
+        <v>348</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>78</v>
+        <v>354</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>78</v>
+        <v>355</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>78</v>
@@ -8074,10 +8185,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8100,17 +8211,15 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>380</v>
+        <v>357</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>381</v>
+        <v>358</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8159,7 +8268,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8168,16 +8277,16 @@
         <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>78</v>
+        <v>360</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8194,10 +8303,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8208,28 +8317,30 @@
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>177</v>
+        <v>363</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>178</v>
+        <v>364</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>179</v>
+        <v>365</v>
       </c>
       <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8277,25 +8388,25 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>180</v>
+        <v>362</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>78</v>
+        <v>367</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>181</v>
+        <v>368</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8312,21 +8423,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
@@ -8338,17 +8449,15 @@
         <v>78</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8397,25 +8506,25 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8432,14 +8541,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>388</v>
+        <v>179</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8452,26 +8561,24 @@
         <v>78</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>389</v>
+        <v>180</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>390</v>
+        <v>181</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8507,19 +8614,19 @@
         <v>78</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>391</v>
+        <v>156</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8537,7 +8644,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8554,10 +8661,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8565,28 +8672,28 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8613,13 +8720,13 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>337</v>
+        <v>374</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -8637,28 +8744,28 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>78</v>
+        <v>378</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>78</v>
+        <v>379</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>78</v>
+        <v>381</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8672,10 +8779,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8683,31 +8790,35 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
@@ -8755,7 +8866,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8770,30 +8881,30 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>78</v>
+        <v>388</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>78</v>
+        <v>391</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8810,24 +8921,26 @@
         <v>78</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>401</v>
+        <v>109</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -8851,13 +8964,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>78</v>
+        <v>374</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>78</v>
+        <v>398</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>78</v>
+        <v>399</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -8890,13 +9003,13 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>78</v>
+        <v>403</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8910,10 +9023,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8933,10 +9046,10 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>406</v>
@@ -8945,7 +9058,7 @@
         <v>407</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8995,7 +9108,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9010,10 +9123,10 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>384</v>
+        <v>152</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9030,10 +9143,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9044,7 +9157,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9053,16 +9166,16 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>380</v>
+        <v>231</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9113,13 +9226,13 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
@@ -9128,13 +9241,13 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>384</v>
+        <v>414</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>78</v>
+        <v>415</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9148,10 +9261,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9162,7 +9275,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -9174,15 +9287,17 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>177</v>
+        <v>417</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>178</v>
+        <v>418</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9231,25 +9346,25 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>180</v>
+        <v>416</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>181</v>
+        <v>421</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9266,21 +9381,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>78</v>
@@ -9292,17 +9407,15 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9351,25 +9464,25 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -9386,14 +9499,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>388</v>
+        <v>179</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9406,26 +9519,24 @@
         <v>78</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>389</v>
+        <v>180</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>390</v>
+        <v>181</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9473,7 +9584,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>391</v>
+        <v>156</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9491,7 +9602,7 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
@@ -9508,42 +9619,46 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9591,25 +9706,25 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9626,10 +9741,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9640,7 +9755,7 @@
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>78</v>
@@ -9652,13 +9767,13 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9685,13 +9800,13 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>78</v>
+        <v>374</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>78</v>
+        <v>432</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>78</v>
+        <v>433</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -9709,13 +9824,13 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>78</v>
@@ -9727,7 +9842,7 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>384</v>
+        <v>421</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9744,10 +9859,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9770,13 +9885,13 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9827,7 +9942,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9845,7 +9960,7 @@
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>384</v>
+        <v>421</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
@@ -9862,10 +9977,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9876,10 +9991,10 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>78</v>
@@ -9888,18 +10003,18 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -9947,16 +10062,16 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>330</v>
+        <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>101</v>
@@ -9965,23 +10080,1095 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AM69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP69" t="s" s="2">
+      <c r="N73" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP78" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP69">
+  <autoFilter ref="A1:AP78">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9991,7 +11178,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
+  <conditionalFormatting sqref="A2:AI77">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA NEW PERSON (file 200) to FHIR PractitionerRole</t>
+    <t>This StructureDefinition contains the maps for VistA file NEW PERSON (#200) to us-core-practitionerrole</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3874,7 +3874,7 @@
         <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>78</v>
@@ -4238,7 +4238,7 @@
         <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>78</v>
@@ -4720,7 +4720,7 @@
         <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>78</v>
@@ -4840,7 +4840,7 @@
         <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>78</v>
@@ -6160,7 +6160,7 @@
         <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>78</v>
@@ -7600,7 +7600,7 @@
         <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -645,7 +645,7 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
-    <t>418: source value from NEW PERSON - TITLE &gt; TITLE – NAME (#200-8 &gt; 3.1-.01)</t>
+    <t>418: source value from NEW PERSON - TITLE &gt; TITLE - NAME (#200-8 &gt; 3.1-.01)</t>
   </si>
   <si>
     <t>SStaff.SStaff.PositionTitle

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -648,8 +648,7 @@
     <t>418: source value from NEW PERSON - TITLE &gt; TITLE - NAME (#200-8 &gt; 3.1-.01)</t>
   </si>
   <si>
-    <t>SStaff.SStaff.PositionTitle
-Staff.Staff.PositionTitle</t>
+    <t>SStaff.SStaff.PositionTitle,Staff.Staff.PositionTitle</t>
   </si>
   <si>
     <t>PractitionerRole.modifierExtension</t>
@@ -852,8 +851,7 @@
     <t>414: reference from NEW PERSON - NAME (#200-.01)</t>
   </si>
   <si>
-    <t>SStaff.PrescribingProvider.StaffName
-SStaff.SStaff.StaffName</t>
+    <t>SStaff.PrescribingProvider.StaffName,SStaff.SStaff.StaffName</t>
   </si>
   <si>
     <t>PractitionerRole.organization</t>
@@ -1231,8 +1229,7 @@
     <t>391: source value from NEW PERSON - EMAIL ADDRESS (#200-.151)</t>
   </si>
   <si>
-    <t>SStaff.PrescribingProvider.EmailAddress
-SStaff.SStaff.EmailAddress</t>
+    <t>SStaff.PrescribingProvider.EmailAddress,SStaff.SStaff.EmailAddress</t>
   </si>
   <si>
     <t>PractitionerRole.telecom.use</t>
@@ -1816,7 +1813,7 @@
     <col min="39" max="39" width="194.47265625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="148.234375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="46.59375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="63.09375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -234,6 +234,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
@@ -244,12 +250,6 @@
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t/>
@@ -639,16 +639,16 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>418: source value from NEW PERSON - TITLE &gt; TITLE - NAME (#200-8 &gt; 3.1-.01)</t>
+  </si>
+  <si>
+    <t>SStaff.SStaff.PositionTitle,Staff.Staff.PositionTitle</t>
+  </si>
+  <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>418: source value from NEW PERSON - TITLE &gt; TITLE - NAME (#200-8 &gt; 3.1-.01)</t>
-  </si>
-  <si>
-    <t>SStaff.SStaff.PositionTitle,Staff.Staff.PositionTitle</t>
   </si>
   <si>
     <t>PractitionerRole.modifierExtension</t>
@@ -717,6 +717,12 @@
     <t>This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
+    <t>412: transform using false on NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EXPIRATION DATE (#200-8932.1 &gt; 200.05-3) case date &lt; now</t>
+  </si>
+  <si>
+    <t>StaffSub.ProviderTypeAssignment.ExpirationDate</t>
+  </si>
+  <si>
     <t>STF-7</t>
   </si>
   <si>
@@ -724,12 +730,6 @@
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>412: transform using false on NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EXPIRATION DATE (#200-8932.1 &gt; 200.05-3) case date &lt; now</t>
-  </si>
-  <si>
-    <t>StaffSub.ProviderTypeAssignment.ExpirationDate</t>
   </si>
   <si>
     <t>PractitionerRole.period</t>
@@ -789,18 +789,18 @@
 </t>
   </si>
   <si>
+    <t>413: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EFFECTIVE DATE (#200-8932.1 &gt; 200.05-2)</t>
+  </si>
+  <si>
+    <t>StaffSub.ProviderTypeAssignment.EffectiveDate</t>
+  </si>
+  <si>
     <t>DR.1</t>
   </si>
   <si>
     <t>./low</t>
   </si>
   <si>
-    <t>413: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EFFECTIVE DATE (#200-8932.1 &gt; 200.05-2)</t>
-  </si>
-  <si>
-    <t>StaffSub.ProviderTypeAssignment.EffectiveDate</t>
-  </si>
-  <si>
     <t>PractitionerRole.period.end</t>
   </si>
   <si>
@@ -819,13 +819,13 @@
     <t>Period.end</t>
   </si>
   <si>
+    <t>416: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EXPIRATION DATE (#200-8932.1 &gt; 200.05-3)</t>
+  </si>
+  <si>
     <t>DR.2</t>
   </si>
   <si>
     <t>./high</t>
-  </si>
-  <si>
-    <t>416: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EXPIRATION DATE (#200-8932.1 &gt; 200.05-3)</t>
   </si>
   <si>
     <t>PractitionerRole.practitioner</t>
@@ -845,13 +845,13 @@
 </t>
   </si>
   <si>
+    <t>414: reference from NEW PERSON - NAME (#200-.01)</t>
+  </si>
+  <si>
+    <t>SStaff.PrescribingProvider.StaffName,SStaff.SStaff.StaffName</t>
+  </si>
+  <si>
     <t>.player</t>
-  </si>
-  <si>
-    <t>414: reference from NEW PERSON - NAME (#200-.01)</t>
-  </si>
-  <si>
-    <t>SStaff.PrescribingProvider.StaffName,SStaff.SStaff.StaffName</t>
   </si>
   <si>
     <t>PractitionerRole.organization</t>
@@ -975,13 +975,13 @@
     <t>Coding.code</t>
   </si>
   <si>
+    <t>1408: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Person Class &gt; PERSON CLASS - X12 CODE (#200-8932.1 &gt; 200.05-.01 &gt; 8932.1-6)</t>
+  </si>
+  <si>
     <t>C*E.1</t>
   </si>
   <si>
     <t>./code</t>
-  </si>
-  <si>
-    <t>1408: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Person Class &gt; PERSON CLASS - X12 CODE (#200-8932.1 &gt; 200.05-.01 &gt; 8932.1-6)</t>
   </si>
   <si>
     <t>PractitionerRole.code.coding.display</t>
@@ -1105,6 +1105,9 @@
     <t>The location(s) at which this practitioner provides care.</t>
   </si>
   <si>
+    <t>422: reference from PROVIDER - PROVIDER (#44.1-.01)</t>
+  </si>
+  <si>
     <t>.performance.ActDefinitionOrEvent.ServiceDeliveryLocation[@classCode = 'SDLOC']</t>
   </si>
   <si>
@@ -1112,9 +1115,6 @@
   </si>
   <si>
     <t>FiveWs.where[x]</t>
-  </si>
-  <si>
-    <t>422: reference from PROVIDER - PROVIDER (#44.1-.01)</t>
   </si>
   <si>
     <t>PractitionerRole.healthcareService</t>
@@ -1217,6 +1217,12 @@
     <t>ContactPoint.value</t>
   </si>
   <si>
+    <t>391: source value from NEW PERSON - EMAIL ADDRESS (#200-.151)</t>
+  </si>
+  <si>
+    <t>SStaff.PrescribingProvider.EmailAddress,SStaff.SStaff.EmailAddress</t>
+  </si>
+  <si>
     <t>XTN.1 (or XTN.12)</t>
   </si>
   <si>
@@ -1224,12 +1230,6 @@
   </si>
   <si>
     <t>./Value</t>
-  </si>
-  <si>
-    <t>391: source value from NEW PERSON - EMAIL ADDRESS (#200-.151)</t>
-  </si>
-  <si>
-    <t>SStaff.PrescribingProvider.EmailAddress,SStaff.SStaff.EmailAddress</t>
   </si>
   <si>
     <t>PractitionerRole.telecom.use</t>
@@ -1808,12 +1808,12 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="85.47265625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="78.58203125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="194.47265625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="148.234375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="63.09375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="148.234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="63.09375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="85.47265625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="78.58203125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="194.47265625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2046,19 +2046,19 @@
         <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>78</v>
@@ -2647,13 +2647,13 @@
         <v>78</v>
       </c>
       <c r="AL7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>78</v>
@@ -2767,13 +2767,13 @@
         <v>78</v>
       </c>
       <c r="AL8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>78</v>
@@ -3121,13 +3121,13 @@
         <v>78</v>
       </c>
       <c r="AL11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>78</v>
@@ -3359,13 +3359,13 @@
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>78</v>
@@ -3477,13 +3477,13 @@
         <v>78</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>78</v>
@@ -3595,13 +3595,13 @@
         <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>78</v>
@@ -3715,13 +3715,13 @@
         <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>78</v>
@@ -3834,16 +3834,16 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>78</v>
@@ -3962,16 +3962,16 @@
         <v>201</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>202</v>
+        <v>78</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>203</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" hidden="true">
@@ -4081,13 +4081,13 @@
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>78</v>
@@ -4198,22 +4198,22 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -4328,13 +4328,13 @@
         <v>226</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>229</v>
@@ -4442,22 +4442,22 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -4563,13 +4563,13 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>78</v>
@@ -4683,13 +4683,13 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>78</v>
@@ -4806,16 +4806,16 @@
         <v>249</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>78</v>
+        <v>250</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>78</v>
+        <v>251</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>250</v>
+        <v>78</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>251</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -4925,19 +4925,19 @@
         <v>258</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AM26" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AN26" t="s" s="2">
-        <v>78</v>
+        <v>260</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>260</v>
+        <v>78</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>229</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -5040,22 +5040,22 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>78</v>
+        <v>268</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>268</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -5161,13 +5161,13 @@
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>78</v>
@@ -5280,19 +5280,19 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>78</v>
@@ -5401,13 +5401,13 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>78</v>
@@ -5521,13 +5521,13 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -5640,16 +5640,16 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -5761,13 +5761,13 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>78</v>
@@ -5881,13 +5881,13 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>78</v>
@@ -6000,16 +6000,16 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>78</v>
@@ -6120,16 +6120,16 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>78</v>
@@ -6243,16 +6243,16 @@
         <v>309</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AM37" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AN37" t="s" s="2">
-        <v>78</v>
+        <v>311</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>311</v>
+        <v>78</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>78</v>
@@ -6360,16 +6360,16 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>78</v>
@@ -6482,16 +6482,16 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>78</v>
@@ -6604,16 +6604,16 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>201</v>
+        <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>78</v>
@@ -6720,19 +6720,19 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>78</v>
@@ -6841,13 +6841,13 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
@@ -6961,13 +6961,13 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>78</v>
@@ -7080,16 +7080,16 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -7201,13 +7201,13 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>78</v>
@@ -7321,13 +7321,13 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -7440,16 +7440,16 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
@@ -7560,16 +7560,16 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>78</v>
@@ -7680,22 +7680,22 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>309</v>
+        <v>343</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AN49" t="s" s="2">
-        <v>78</v>
+        <v>311</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>343</v>
+        <v>78</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -7800,16 +7800,16 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
@@ -7922,16 +7922,16 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>78</v>
@@ -8044,16 +8044,16 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>201</v>
+        <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>78</v>
@@ -8162,22 +8162,22 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>78</v>
+        <v>352</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>352</v>
+        <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AO53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="54" hidden="true">
@@ -8280,16 +8280,16 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8403,13 +8403,13 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -8521,13 +8521,13 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>78</v>
@@ -8641,13 +8641,13 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -8756,19 +8756,19 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>78</v>
@@ -8887,13 +8887,13 @@
         <v>390</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>78</v>
+        <v>391</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>392</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" hidden="true">
@@ -9000,19 +9000,19 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>78</v>
@@ -9120,16 +9120,16 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9238,19 +9238,19 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="AL62" t="s" s="2">
+      <c r="AN62" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>78</v>
@@ -9361,13 +9361,13 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9479,13 +9479,13 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -9599,13 +9599,13 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -9721,13 +9721,13 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -9839,13 +9839,13 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -9957,13 +9957,13 @@
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -10077,13 +10077,13 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -10197,13 +10197,13 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -10315,13 +10315,13 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10433,13 +10433,13 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10553,13 +10553,13 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>78</v>
@@ -10675,13 +10675,13 @@
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>78</v>
@@ -10793,13 +10793,13 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
@@ -10911,13 +10911,13 @@
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -11029,13 +11029,13 @@
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>78</v>
@@ -11149,13 +11149,13 @@
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2995" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2995" uniqueCount="466">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -717,7 +717,7 @@
     <t>This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
-    <t>412: transform using false on NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EXPIRATION DATE (#200-8932.1 &gt; 200.05-3) case date &lt; now</t>
+    <t>412: fixed value = false when NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EXPIRATION DATE (#200-8932.1 &gt; 200.05-3) case date &lt; now</t>
   </si>
   <si>
     <t>StaffSub.ProviderTypeAssignment.ExpirationDate</t>
@@ -865,6 +865,9 @@
   </si>
   <si>
     <t>The organization where the Practitioner performs the roles associated.</t>
+  </si>
+  <si>
+    <t>1411: reference from NEW PERSON - DIVISION (#200-16)</t>
   </si>
   <si>
     <t>.scoper</t>
@@ -5158,7 +5161,7 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>78</v>
@@ -5167,7 +5170,7 @@
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>78</v>
@@ -5178,10 +5181,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5207,16 +5210,16 @@
         <v>166</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -5241,13 +5244,13 @@
         <v>78</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>78</v>
@@ -5265,7 +5268,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5286,10 +5289,10 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>237</v>
@@ -5300,10 +5303,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5418,10 +5421,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5538,10 +5541,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5660,10 +5663,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5778,10 +5781,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5898,10 +5901,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5927,16 +5930,16 @@
         <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5985,7 +5988,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6006,10 +6009,10 @@
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>78</v>
@@ -6020,10 +6023,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6049,13 +6052,13 @@
         <v>176</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6105,7 +6108,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6126,10 +6129,10 @@
         <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>78</v>
@@ -6140,10 +6143,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6169,14 +6172,14 @@
         <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6225,7 +6228,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6240,16 +6243,16 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>78</v>
@@ -6260,10 +6263,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6289,14 +6292,14 @@
         <v>176</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6345,7 +6348,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6366,10 +6369,10 @@
         <v>78</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>78</v>
@@ -6380,10 +6383,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6409,16 +6412,16 @@
         <v>219</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6467,7 +6470,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6488,10 +6491,10 @@
         <v>78</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>78</v>
@@ -6502,10 +6505,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6624,10 +6627,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6653,10 +6656,10 @@
         <v>166</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6683,11 +6686,11 @@
         <v>78</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>78</v>
@@ -6705,7 +6708,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6726,13 +6729,13 @@
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>78</v>
@@ -6740,10 +6743,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6858,10 +6861,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6978,10 +6981,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7100,10 +7103,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7218,10 +7221,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7338,10 +7341,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7367,16 +7370,16 @@
         <v>103</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
@@ -7425,7 +7428,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7446,10 +7449,10 @@
         <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
@@ -7460,10 +7463,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7489,13 +7492,13 @@
         <v>176</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7545,7 +7548,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7566,10 +7569,10 @@
         <v>78</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>78</v>
@@ -7580,10 +7583,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7609,14 +7612,14 @@
         <v>109</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7665,7 +7668,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7680,16 +7683,16 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
@@ -7700,10 +7703,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7729,14 +7732,14 @@
         <v>176</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7785,7 +7788,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7806,10 +7809,10 @@
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
@@ -7820,10 +7823,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7849,16 +7852,16 @@
         <v>219</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -7907,7 +7910,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7928,10 +7931,10 @@
         <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>78</v>
@@ -7942,10 +7945,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8064,10 +8067,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8090,13 +8093,13 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8147,7 +8150,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8162,7 +8165,7 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>78</v>
@@ -8171,21 +8174,21 @@
         <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8208,13 +8211,13 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8265,7 +8268,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8286,10 +8289,10 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8300,10 +8303,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8326,17 +8329,17 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8385,7 +8388,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8394,7 +8397,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>101</v>
@@ -8409,7 +8412,7 @@
         <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -8420,10 +8423,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8538,10 +8541,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8658,10 +8661,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8687,10 +8690,10 @@
         <v>109</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8717,13 +8720,13 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -8741,7 +8744,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8750,7 +8753,7 @@
         <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>101</v>
@@ -8762,13 +8765,13 @@
         <v>78</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>78</v>
@@ -8776,10 +8779,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8805,16 +8808,16 @@
         <v>176</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8863,7 +8866,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8878,19 +8881,19 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>78</v>
@@ -8898,10 +8901,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8927,16 +8930,16 @@
         <v>109</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8961,13 +8964,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -8985,7 +8988,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9006,13 +9009,13 @@
         <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>78</v>
@@ -9020,10 +9023,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9046,16 +9049,16 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9105,7 +9108,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9140,10 +9143,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9169,10 +9172,10 @@
         <v>231</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9223,7 +9226,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9247,10 +9250,10 @@
         <v>132</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>78</v>
@@ -9258,10 +9261,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9284,16 +9287,16 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9343,7 +9346,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9367,7 +9370,7 @@
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9378,10 +9381,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9496,10 +9499,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9616,14 +9619,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9645,10 +9648,10 @@
         <v>134</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>182</v>
@@ -9703,7 +9706,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9738,10 +9741,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9767,10 +9770,10 @@
         <v>109</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9797,13 +9800,13 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -9821,7 +9824,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9845,7 +9848,7 @@
         <v>78</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -9856,10 +9859,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9885,10 +9888,10 @@
         <v>219</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9939,7 +9942,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9963,7 +9966,7 @@
         <v>78</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -9974,10 +9977,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10000,16 +10003,16 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10059,7 +10062,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10083,7 +10086,7 @@
         <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -10094,10 +10097,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10120,16 +10123,16 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10179,7 +10182,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10203,7 +10206,7 @@
         <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -10214,10 +10217,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10240,13 +10243,13 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10297,7 +10300,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10321,7 +10324,7 @@
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10332,10 +10335,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10450,10 +10453,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10570,14 +10573,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10599,10 +10602,10 @@
         <v>134</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>182</v>
@@ -10657,7 +10660,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10692,10 +10695,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10721,10 +10724,10 @@
         <v>176</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10775,7 +10778,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>89</v>
@@ -10810,10 +10813,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10839,10 +10842,10 @@
         <v>231</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10893,7 +10896,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10917,7 +10920,7 @@
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -10928,10 +10931,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10957,10 +10960,10 @@
         <v>176</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11011,7 +11014,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11035,7 +11038,7 @@
         <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>78</v>
@@ -11046,10 +11049,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11072,17 +11075,17 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11131,7 +11134,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11140,7 +11143,7 @@
         <v>80</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>101</v>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file NEW PERSON (#200) to us-core-practitionerrole</t>
+    <t>This StructureDefinition contains the maps for VistA file NEW PERSON (200) to us-core-practitionerrole</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -639,7 +639,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>418: source value from NEW PERSON - TITLE &gt; TITLE - NAME (#200-8 &gt; 3.1-.01)</t>
+    <t>418: source value from NEW PERSON - TITLE &gt; TITLE - NAME (200-8 &gt; 3.1-.01)</t>
   </si>
   <si>
     <t>SStaff.SStaff.PositionTitle,Staff.Staff.PositionTitle</t>
@@ -717,7 +717,7 @@
     <t>This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
-    <t>412: fixed value = false when NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EXPIRATION DATE (#200-8932.1 &gt; 200.05-3) case date &lt; now</t>
+    <t>412: fixed value = false when NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EXPIRATION DATE (200-8932.1 &gt; 200.05-3) case date &lt; now</t>
   </si>
   <si>
     <t>StaffSub.ProviderTypeAssignment.ExpirationDate</t>
@@ -789,7 +789,7 @@
 </t>
   </si>
   <si>
-    <t>413: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EFFECTIVE DATE (#200-8932.1 &gt; 200.05-2)</t>
+    <t>413: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EFFECTIVE DATE (200-8932.1 &gt; 200.05-2)</t>
   </si>
   <si>
     <t>StaffSub.ProviderTypeAssignment.EffectiveDate</t>
@@ -819,7 +819,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>416: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EXPIRATION DATE (#200-8932.1 &gt; 200.05-3)</t>
+    <t>416: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EXPIRATION DATE (200-8932.1 &gt; 200.05-3)</t>
   </si>
   <si>
     <t>DR.2</t>
@@ -845,7 +845,7 @@
 </t>
   </si>
   <si>
-    <t>414: reference from NEW PERSON - NAME (#200-.01)</t>
+    <t>414: reference from NEW PERSON - NAME (200-.01)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.StaffName,SStaff.SStaff.StaffName</t>
@@ -867,7 +867,7 @@
     <t>The organization where the Practitioner performs the roles associated.</t>
   </si>
   <si>
-    <t>1411: reference from NEW PERSON - DIVISION (#200-16)</t>
+    <t>1411: reference from NEW PERSON - DIVISION (200-16)</t>
   </si>
   <si>
     <t>.scoper</t>
@@ -978,7 +978,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1408: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Person Class &gt; PERSON CLASS - X12 CODE (#200-8932.1 &gt; 200.05-.01 &gt; 8932.1-6)</t>
+    <t>1408: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Person Class &gt; PERSON CLASS - X12 CODE (200-8932.1 &gt; 200.05-.01 &gt; 8932.1-6)</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1080,7 +1080,7 @@
     <t>PractitionerRole.specialty.coding.code</t>
   </si>
   <si>
-    <t>419: source value from PERSON CLASS - X12 CODE (#8932.1-6)</t>
+    <t>419: source value from PERSON CLASS - X12 CODE (8932.1-6)</t>
   </si>
   <si>
     <t>Dim.ProviderType.X12Code</t>
@@ -1108,7 +1108,7 @@
     <t>The location(s) at which this practitioner provides care.</t>
   </si>
   <si>
-    <t>422: reference from PROVIDER - PROVIDER (#44.1-.01)</t>
+    <t>422: reference from PROVIDER - PROVIDER (44.1-.01)</t>
   </si>
   <si>
     <t>.performance.ActDefinitionOrEvent.ServiceDeliveryLocation[@classCode = 'SDLOC']</t>
@@ -1220,7 +1220,7 @@
     <t>ContactPoint.value</t>
   </si>
   <si>
-    <t>391: source value from NEW PERSON - EMAIL ADDRESS (#200-.151)</t>
+    <t>391: source value from NEW PERSON - EMAIL ADDRESS (200-.151)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.EmailAddress,SStaff.SStaff.EmailAddress</t>
@@ -1811,7 +1811,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="148.234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="146.6953125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="63.09375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="85.47265625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="78.58203125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -717,7 +717,7 @@
     <t>This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
-    <t>412: fixed value = false when NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EXPIRATION DATE (200-8932.1 &gt; 200.05-3) case date &lt; now</t>
+    <t>412: fixed value = false when NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Expiration Date (200-8932.1 &gt; 200.05-3) case date &lt; now</t>
   </si>
   <si>
     <t>StaffSub.ProviderTypeAssignment.ExpirationDate</t>
@@ -789,7 +789,7 @@
 </t>
   </si>
   <si>
-    <t>413: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EFFECTIVE DATE (200-8932.1 &gt; 200.05-2)</t>
+    <t>413: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Effective Date (200-8932.1 &gt; 200.05-2)</t>
   </si>
   <si>
     <t>StaffSub.ProviderTypeAssignment.EffectiveDate</t>
@@ -819,7 +819,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>416: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - EXPIRATION DATE (200-8932.1 &gt; 200.05-3)</t>
+    <t>416: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Expiration Date (200-8932.1 &gt; 200.05-3)</t>
   </si>
   <si>
     <t>DR.2</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2995" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2995" uniqueCount="467">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -720,7 +720,7 @@
     <t>412: fixed value = false when NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Expiration Date (200-8932.1 &gt; 200.05-3) case date &lt; now</t>
   </si>
   <si>
-    <t>StaffSub.ProviderTypeAssignment.ExpirationDate</t>
+    <t>StaffSub.ProviderTypeAssignment.ExpirationDateTime</t>
   </si>
   <si>
     <t>STF-7</t>
@@ -792,7 +792,7 @@
     <t>413: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Effective Date (200-8932.1 &gt; 200.05-2)</t>
   </si>
   <si>
-    <t>StaffSub.ProviderTypeAssignment.EffectiveDate</t>
+    <t>StaffSub.ProviderTypeAssignment.EffectiveDateTime</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -1109,6 +1109,9 @@
   </si>
   <si>
     <t>422: reference from PROVIDER - PROVIDER (44.1-.01)</t>
+  </si>
+  <si>
+    <t>Dim.LocationProvider.StaffIEN</t>
   </si>
   <si>
     <t>.performance.ActDefinitionOrEvent.ServiceDeliveryLocation[@classCode = 'SDLOC']</t>
@@ -8168,27 +8171,27 @@
         <v>353</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>78</v>
+        <v>354</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8211,13 +8214,13 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8268,7 +8271,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8289,10 +8292,10 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8303,10 +8306,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8329,17 +8332,17 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8388,7 +8391,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8397,7 +8400,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>101</v>
@@ -8412,7 +8415,7 @@
         <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -8423,10 +8426,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8541,10 +8544,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8661,10 +8664,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8690,10 +8693,10 @@
         <v>109</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8720,13 +8723,13 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -8744,7 +8747,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8753,7 +8756,7 @@
         <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>101</v>
@@ -8765,13 +8768,13 @@
         <v>78</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>78</v>
@@ -8779,10 +8782,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8808,16 +8811,16 @@
         <v>176</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8866,7 +8869,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8881,19 +8884,19 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>78</v>
@@ -8901,10 +8904,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8930,16 +8933,16 @@
         <v>109</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8964,13 +8967,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -8988,7 +8991,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9009,13 +9012,13 @@
         <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>78</v>
@@ -9023,10 +9026,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9049,16 +9052,16 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9108,7 +9111,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9143,10 +9146,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9172,10 +9175,10 @@
         <v>231</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9226,7 +9229,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9250,10 +9253,10 @@
         <v>132</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>78</v>
@@ -9261,10 +9264,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9287,16 +9290,16 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9346,7 +9349,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9370,7 +9373,7 @@
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9381,10 +9384,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9499,10 +9502,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9619,14 +9622,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9648,10 +9651,10 @@
         <v>134</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>182</v>
@@ -9706,7 +9709,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9741,10 +9744,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9770,10 +9773,10 @@
         <v>109</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9800,13 +9803,13 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -9824,7 +9827,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9848,7 +9851,7 @@
         <v>78</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -9859,10 +9862,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9888,10 +9891,10 @@
         <v>219</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9942,7 +9945,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9966,7 +9969,7 @@
         <v>78</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -9977,10 +9980,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10003,16 +10006,16 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10062,7 +10065,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10086,7 +10089,7 @@
         <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -10097,10 +10100,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10123,16 +10126,16 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10182,7 +10185,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10206,7 +10209,7 @@
         <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -10217,10 +10220,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10243,13 +10246,13 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10300,7 +10303,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10324,7 +10327,7 @@
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10335,10 +10338,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10453,10 +10456,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10573,14 +10576,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10602,10 +10605,10 @@
         <v>134</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>182</v>
@@ -10660,7 +10663,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10695,10 +10698,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10724,10 +10727,10 @@
         <v>176</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10778,7 +10781,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>89</v>
@@ -10813,10 +10816,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10842,10 +10845,10 @@
         <v>231</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10896,7 +10899,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10920,7 +10923,7 @@
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -10931,10 +10934,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10960,10 +10963,10 @@
         <v>176</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11014,7 +11017,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11038,7 +11041,7 @@
         <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>78</v>
@@ -11049,10 +11052,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11075,17 +11078,17 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11134,7 +11137,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11143,7 +11146,7 @@
         <v>80</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>101</v>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5426" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5426" uniqueCount="574">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1092,10 +1092,7 @@
     <t>PractitionerRole.specialty.coding.code</t>
   </si>
   <si>
-    <t>419: source value from PERSON CLASS - X12 CODE (8932.1-6)</t>
-  </si>
-  <si>
-    <t>Dim.ProviderType.X12Code</t>
+    <t>419: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Person Class &gt; PERSON CLASS - X12 CODE (200-8932.1 &gt; 200.05-.01 &gt; 8932.1-6)</t>
   </si>
   <si>
     <t>PractitionerRole.specialty.coding.display</t>
@@ -8014,7 +8011,7 @@
         <v>348</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>349</v>
+        <v>78</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>313</v>
@@ -8031,10 +8028,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8131,7 +8128,7 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>78</v>
@@ -8151,10 +8148,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8273,10 +8270,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8395,10 +8392,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8421,13 +8418,13 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8478,7 +8475,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8493,30 +8490,30 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AM53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AM53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AO53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>362</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8539,13 +8536,13 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8596,7 +8593,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8617,10 +8614,10 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8631,10 +8628,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8657,17 +8654,17 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8704,7 +8701,7 @@
         <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
@@ -8714,7 +8711,7 @@
         <v>138</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8723,7 +8720,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>101</v>
@@ -8738,7 +8735,7 @@
         <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -8749,10 +8746,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8867,10 +8864,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8987,10 +8984,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9016,10 +9013,10 @@
         <v>109</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9046,40 +9043,40 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Y58" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="Y58" t="s" s="2">
+      <c r="Z58" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z58" t="s" s="2">
+      <c r="AA58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AA58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF58" t="s" s="2">
+      <c r="AG58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI58" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>101</v>
@@ -9091,13 +9088,13 @@
         <v>78</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>78</v>
@@ -9105,10 +9102,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9134,16 +9131,16 @@
         <v>176</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -9192,7 +9189,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9213,13 +9210,13 @@
         <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>78</v>
@@ -9227,10 +9224,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9256,16 +9253,16 @@
         <v>109</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9290,31 +9287,31 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="Z60" t="s" s="2">
+      <c r="AA60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9335,13 +9332,13 @@
         <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>78</v>
@@ -9349,10 +9346,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9375,16 +9372,16 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9434,7 +9431,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9469,10 +9466,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9498,10 +9495,10 @@
         <v>231</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9552,7 +9549,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9576,10 +9573,10 @@
         <v>132</v>
       </c>
       <c r="AN62" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>78</v>
@@ -9587,13 +9584,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C63" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>78</v>
@@ -9615,17 +9612,17 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9674,7 +9671,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9683,7 +9680,7 @@
         <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>101</v>
@@ -9698,7 +9695,7 @@
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9709,10 +9706,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9827,10 +9824,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9947,10 +9944,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9976,10 +9973,10 @@
         <v>109</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9991,7 +9988,7 @@
         <v>78</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>78</v>
@@ -10006,58 +10003,58 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Y66" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="Y66" t="s" s="2">
+      <c r="Z66" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z66" t="s" s="2">
+      <c r="AA66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AA66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF66" t="s" s="2">
+      <c r="AG66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI66" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>78</v>
@@ -10065,10 +10062,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10094,16 +10091,16 @@
         <v>176</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -10152,7 +10149,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10167,19 +10164,19 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL67" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AL67" t="s" s="2">
-        <v>431</v>
-      </c>
       <c r="AM67" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>78</v>
@@ -10187,10 +10184,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10216,16 +10213,16 @@
         <v>109</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10235,7 +10232,7 @@
         <v>78</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>78</v>
@@ -10250,31 +10247,31 @@
         <v>78</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="Z68" t="s" s="2">
+      <c r="AA68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10289,19 +10286,19 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>78</v>
@@ -10309,10 +10306,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10335,16 +10332,16 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10394,7 +10391,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10429,10 +10426,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10458,10 +10455,10 @@
         <v>231</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10512,7 +10509,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10536,10 +10533,10 @@
         <v>132</v>
       </c>
       <c r="AN70" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>78</v>
@@ -10547,13 +10544,13 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C71" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>78</v>
@@ -10575,17 +10572,17 @@
         <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10634,7 +10631,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10643,7 +10640,7 @@
         <v>80</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>101</v>
@@ -10658,7 +10655,7 @@
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10669,10 +10666,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10787,10 +10784,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10907,10 +10904,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10936,10 +10933,10 @@
         <v>109</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10951,7 +10948,7 @@
         <v>78</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>78</v>
@@ -10966,58 +10963,58 @@
         <v>78</v>
       </c>
       <c r="X74" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Y74" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="Y74" t="s" s="2">
+      <c r="Z74" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z74" t="s" s="2">
+      <c r="AA74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AA74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF74" t="s" s="2">
+      <c r="AG74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI74" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>78</v>
@@ -11025,10 +11022,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11054,16 +11051,16 @@
         <v>176</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -11112,7 +11109,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11127,19 +11124,19 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL75" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AL75" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="AM75" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>78</v>
@@ -11147,10 +11144,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11176,16 +11173,16 @@
         <v>109</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -11210,31 +11207,31 @@
         <v>78</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="Z76" t="s" s="2">
+      <c r="AA76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11255,13 +11252,13 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>78</v>
@@ -11269,10 +11266,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11295,16 +11292,16 @@
         <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11354,7 +11351,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11389,10 +11386,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11418,10 +11415,10 @@
         <v>231</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11472,7 +11469,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11496,10 +11493,10 @@
         <v>132</v>
       </c>
       <c r="AN78" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO78" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>78</v>
@@ -11507,13 +11504,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>78</v>
@@ -11535,17 +11532,17 @@
         <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11594,7 +11591,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11603,7 +11600,7 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>101</v>
@@ -11618,7 +11615,7 @@
         <v>78</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>78</v>
@@ -11629,10 +11626,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11747,10 +11744,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11867,10 +11864,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11896,10 +11893,10 @@
         <v>109</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11911,7 +11908,7 @@
         <v>78</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>78</v>
@@ -11926,58 +11923,58 @@
         <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Y82" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="Y82" t="s" s="2">
+      <c r="Z82" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z82" t="s" s="2">
+      <c r="AA82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AA82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF82" t="s" s="2">
+      <c r="AG82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI82" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AN82" t="s" s="2">
+      <c r="AO82" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>78</v>
@@ -11985,10 +11982,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12014,16 +12011,16 @@
         <v>176</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -12072,7 +12069,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12087,19 +12084,19 @@
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AL83" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="AL83" t="s" s="2">
-        <v>457</v>
-      </c>
       <c r="AM83" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AN83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>78</v>
@@ -12107,10 +12104,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12136,16 +12133,16 @@
         <v>109</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -12170,31 +12167,31 @@
         <v>78</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="Z84" t="s" s="2">
+      <c r="AA84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12215,13 +12212,13 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AN84" t="s" s="2">
+      <c r="AO84" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>78</v>
@@ -12229,10 +12226,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12255,16 +12252,16 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12314,7 +12311,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12349,10 +12346,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12378,10 +12375,10 @@
         <v>231</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12432,7 +12429,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12456,10 +12453,10 @@
         <v>132</v>
       </c>
       <c r="AN86" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO86" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>78</v>
@@ -12467,13 +12464,13 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C87" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C87" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>78</v>
@@ -12495,17 +12492,17 @@
         <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
@@ -12554,7 +12551,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12563,7 +12560,7 @@
         <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>101</v>
@@ -12578,7 +12575,7 @@
         <v>78</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>78</v>
@@ -12589,10 +12586,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12707,10 +12704,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12827,10 +12824,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12856,10 +12853,10 @@
         <v>109</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12871,7 +12868,7 @@
         <v>78</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>78</v>
@@ -12886,58 +12883,58 @@
         <v>78</v>
       </c>
       <c r="X90" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Y90" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="Y90" t="s" s="2">
+      <c r="Z90" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z90" t="s" s="2">
+      <c r="AA90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AA90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF90" t="s" s="2">
+      <c r="AG90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI90" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AN90" t="s" s="2">
+      <c r="AO90" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>78</v>
@@ -12945,10 +12942,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12974,16 +12971,16 @@
         <v>176</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -13032,7 +13029,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13047,19 +13044,19 @@
         <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AL91" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AL91" t="s" s="2">
-        <v>469</v>
-      </c>
       <c r="AM91" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AN91" t="s" s="2">
+      <c r="AO91" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>78</v>
@@ -13067,10 +13064,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13096,16 +13093,16 @@
         <v>109</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -13115,7 +13112,7 @@
         <v>78</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>78</v>
@@ -13130,31 +13127,31 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="Z92" t="s" s="2">
+      <c r="AA92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13169,19 +13166,19 @@
         <v>101</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AN92" t="s" s="2">
+      <c r="AO92" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>78</v>
@@ -13189,10 +13186,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13215,16 +13212,16 @@
         <v>90</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13274,7 +13271,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13309,10 +13306,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13338,10 +13335,10 @@
         <v>231</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13392,7 +13389,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13416,10 +13413,10 @@
         <v>132</v>
       </c>
       <c r="AN94" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO94" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>78</v>
@@ -13427,13 +13424,13 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C95" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>78</v>
@@ -13455,17 +13452,17 @@
         <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>78</v>
@@ -13514,7 +13511,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13523,7 +13520,7 @@
         <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>101</v>
@@ -13538,7 +13535,7 @@
         <v>78</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>78</v>
@@ -13549,10 +13546,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13667,10 +13664,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13787,10 +13784,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13816,10 +13813,10 @@
         <v>109</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13831,7 +13828,7 @@
         <v>78</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>78</v>
@@ -13846,58 +13843,58 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Y98" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="Y98" t="s" s="2">
+      <c r="Z98" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z98" t="s" s="2">
+      <c r="AA98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AA98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF98" t="s" s="2">
+      <c r="AG98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI98" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AN98" t="s" s="2">
+      <c r="AO98" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>78</v>
@@ -13905,10 +13902,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13934,16 +13931,16 @@
         <v>176</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13992,7 +13989,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14007,19 +14004,19 @@
         <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL99" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AL99" t="s" s="2">
-        <v>483</v>
-      </c>
       <c r="AM99" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AN99" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AN99" t="s" s="2">
+      <c r="AO99" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>78</v>
@@ -14027,10 +14024,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14056,16 +14053,16 @@
         <v>109</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -14075,7 +14072,7 @@
         <v>78</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>78</v>
@@ -14090,31 +14087,31 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Y100" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z100" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="Z100" t="s" s="2">
+      <c r="AA100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14129,19 +14126,19 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM100" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN100" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AN100" t="s" s="2">
+      <c r="AO100" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>78</v>
@@ -14149,10 +14146,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14175,16 +14172,16 @@
         <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14234,7 +14231,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14269,10 +14266,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14298,10 +14295,10 @@
         <v>231</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14352,7 +14349,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14376,10 +14373,10 @@
         <v>132</v>
       </c>
       <c r="AN102" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO102" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>78</v>
@@ -14387,13 +14384,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C103" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>78</v>
@@ -14415,17 +14412,17 @@
         <v>90</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14474,7 +14471,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14483,7 +14480,7 @@
         <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>101</v>
@@ -14498,7 +14495,7 @@
         <v>78</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>78</v>
@@ -14509,10 +14506,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14627,10 +14624,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14747,10 +14744,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14776,10 +14773,10 @@
         <v>109</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14791,7 +14788,7 @@
         <v>78</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>78</v>
@@ -14806,58 +14803,58 @@
         <v>78</v>
       </c>
       <c r="X106" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Y106" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="Y106" t="s" s="2">
+      <c r="Z106" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z106" t="s" s="2">
+      <c r="AA106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF106" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AA106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF106" t="s" s="2">
+      <c r="AG106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI106" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM106" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AN106" t="s" s="2">
+      <c r="AO106" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>78</v>
@@ -14865,10 +14862,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14894,16 +14891,16 @@
         <v>176</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -14952,7 +14949,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14967,19 +14964,19 @@
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AL107" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AL107" t="s" s="2">
-        <v>497</v>
-      </c>
       <c r="AM107" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AN107" t="s" s="2">
+      <c r="AO107" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>78</v>
@@ -14987,10 +14984,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15016,16 +15013,16 @@
         <v>109</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -15050,31 +15047,31 @@
         <v>78</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Y108" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z108" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="Z108" t="s" s="2">
+      <c r="AA108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF108" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15095,13 +15092,13 @@
         <v>78</v>
       </c>
       <c r="AM108" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AN108" t="s" s="2">
+      <c r="AO108" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>78</v>
@@ -15109,10 +15106,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15135,16 +15132,16 @@
         <v>90</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15194,7 +15191,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15229,10 +15226,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15258,10 +15255,10 @@
         <v>231</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15312,7 +15309,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15336,10 +15333,10 @@
         <v>132</v>
       </c>
       <c r="AN110" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO110" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>78</v>
@@ -15347,13 +15344,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C111" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>78</v>
@@ -15375,17 +15372,17 @@
         <v>90</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -15434,7 +15431,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15443,7 +15440,7 @@
         <v>80</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>101</v>
@@ -15458,7 +15455,7 @@
         <v>78</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>78</v>
@@ -15469,10 +15466,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15587,10 +15584,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15707,10 +15704,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15736,10 +15733,10 @@
         <v>109</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15751,7 +15748,7 @@
         <v>78</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>78</v>
@@ -15766,58 +15763,58 @@
         <v>78</v>
       </c>
       <c r="X114" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Y114" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="Y114" t="s" s="2">
+      <c r="Z114" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z114" t="s" s="2">
+      <c r="AA114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF114" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AA114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF114" t="s" s="2">
+      <c r="AG114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI114" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM114" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AN114" t="s" s="2">
+      <c r="AO114" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>78</v>
@@ -15825,10 +15822,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15854,16 +15851,16 @@
         <v>176</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>78</v>
@@ -15912,7 +15909,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -15927,19 +15924,19 @@
         <v>101</v>
       </c>
       <c r="AK115" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AL115" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AL115" t="s" s="2">
-        <v>509</v>
-      </c>
       <c r="AM115" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AN115" t="s" s="2">
+      <c r="AO115" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>78</v>
@@ -15947,10 +15944,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15976,16 +15973,16 @@
         <v>109</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N116" t="s" s="2">
+      <c r="O116" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -16010,31 +16007,31 @@
         <v>78</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Y116" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z116" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="Z116" t="s" s="2">
+      <c r="AA116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF116" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16055,13 +16052,13 @@
         <v>78</v>
       </c>
       <c r="AM116" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN116" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AN116" t="s" s="2">
+      <c r="AO116" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>78</v>
@@ -16069,10 +16066,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16095,16 +16092,16 @@
         <v>90</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="M117" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M117" t="s" s="2">
+      <c r="N117" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16154,7 +16151,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16189,10 +16186,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16218,10 +16215,10 @@
         <v>231</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16272,7 +16269,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16296,10 +16293,10 @@
         <v>132</v>
       </c>
       <c r="AN118" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO118" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AP118" t="s" s="2">
         <v>78</v>
@@ -16307,13 +16304,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C119" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>78</v>
@@ -16335,17 +16332,17 @@
         <v>90</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>78</v>
@@ -16394,7 +16391,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16403,7 +16400,7 @@
         <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>101</v>
@@ -16418,7 +16415,7 @@
         <v>78</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>78</v>
@@ -16429,10 +16426,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16547,10 +16544,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16667,10 +16664,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16696,10 +16693,10 @@
         <v>109</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16711,7 +16708,7 @@
         <v>78</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>78</v>
@@ -16726,58 +16723,58 @@
         <v>78</v>
       </c>
       <c r="X122" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Y122" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="Y122" t="s" s="2">
+      <c r="Z122" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z122" t="s" s="2">
+      <c r="AA122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF122" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AA122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF122" t="s" s="2">
+      <c r="AG122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI122" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM122" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AN122" t="s" s="2">
+      <c r="AO122" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>78</v>
@@ -16785,10 +16782,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16814,16 +16811,16 @@
         <v>176</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16872,7 +16869,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16887,19 +16884,19 @@
         <v>101</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AL123" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AL123" t="s" s="2">
-        <v>522</v>
-      </c>
       <c r="AM123" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AN123" t="s" s="2">
+      <c r="AO123" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>78</v>
@@ -16907,10 +16904,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16936,16 +16933,16 @@
         <v>109</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N124" t="s" s="2">
+      <c r="O124" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -16970,31 +16967,31 @@
         <v>78</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Y124" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z124" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="Z124" t="s" s="2">
+      <c r="AA124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF124" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17015,13 +17012,13 @@
         <v>78</v>
       </c>
       <c r="AM124" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AN124" t="s" s="2">
+      <c r="AO124" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>78</v>
@@ -17029,10 +17026,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17055,16 +17052,16 @@
         <v>90</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L125" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="M125" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17114,7 +17111,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17149,10 +17146,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17178,10 +17175,10 @@
         <v>231</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17232,7 +17229,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17256,10 +17253,10 @@
         <v>132</v>
       </c>
       <c r="AN126" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO126" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AP126" t="s" s="2">
         <v>78</v>
@@ -17267,10 +17264,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17293,16 +17290,16 @@
         <v>78</v>
       </c>
       <c r="K127" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="L127" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="L127" t="s" s="2">
+      <c r="M127" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17352,7 +17349,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17376,7 +17373,7 @@
         <v>78</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>78</v>
@@ -17387,10 +17384,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17505,10 +17502,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17625,14 +17622,14 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -17654,10 +17651,10 @@
         <v>134</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>182</v>
@@ -17712,7 +17709,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17747,10 +17744,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17776,10 +17773,10 @@
         <v>109</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17806,14 +17803,14 @@
         <v>78</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Y131" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="Z131" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="Z131" t="s" s="2">
-        <v>543</v>
-      </c>
       <c r="AA131" t="s" s="2">
         <v>78</v>
       </c>
@@ -17830,7 +17827,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17854,7 +17851,7 @@
         <v>78</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>78</v>
@@ -17865,10 +17862,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17894,10 +17891,10 @@
         <v>219</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17948,7 +17945,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -17972,7 +17969,7 @@
         <v>78</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>78</v>
@@ -17983,10 +17980,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18009,16 +18006,16 @@
         <v>78</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18068,7 +18065,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18092,7 +18089,7 @@
         <v>78</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>78</v>
@@ -18103,10 +18100,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18129,16 +18126,16 @@
         <v>78</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M134" t="s" s="2">
-        <v>554</v>
-      </c>
       <c r="N134" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18188,7 +18185,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18212,7 +18209,7 @@
         <v>78</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>78</v>
@@ -18223,10 +18220,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18249,13 +18246,13 @@
         <v>78</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18306,7 +18303,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18330,7 +18327,7 @@
         <v>78</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>78</v>
@@ -18341,10 +18338,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18459,10 +18456,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18579,14 +18576,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -18608,10 +18605,10 @@
         <v>134</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>182</v>
@@ -18666,7 +18663,7 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -18701,10 +18698,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18730,10 +18727,10 @@
         <v>176</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -18784,7 +18781,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>89</v>
@@ -18819,10 +18816,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18848,10 +18845,10 @@
         <v>231</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18902,7 +18899,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18926,7 +18923,7 @@
         <v>78</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>78</v>
@@ -18937,10 +18934,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18966,10 +18963,10 @@
         <v>176</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19020,7 +19017,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19044,7 +19041,7 @@
         <v>78</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>78</v>
@@ -19055,10 +19052,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19081,17 +19078,17 @@
         <v>78</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="L142" t="s" s="2">
+      <c r="M142" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
@@ -19140,7 +19137,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19149,7 +19146,7 @@
         <v>80</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>101</v>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1092,7 +1092,7 @@
     <t>PractitionerRole.specialty.coding.code</t>
   </si>
   <si>
-    <t>419: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Person Class &gt; PERSON CLASS - X12 CODE (200-8932.1 &gt; 200.05-.01 &gt; 8932.1-6)</t>
+    <t>419: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - X12 CODE (200-8932.1 &gt; 200.05-.01 &gt; 8932.1-6)</t>
   </si>
   <si>
     <t>PractitionerRole.specialty.coding.display</t>
@@ -1120,7 +1120,7 @@
     <t>The location(s) at which this practitioner provides care.</t>
   </si>
   <si>
-    <t>422: reference from PROVIDER - PROVIDER (44.1-.01)</t>
+    <t>422: reference from HOSPITAL LOCATION - PROVIDER (44.1-.01)</t>
   </si>
   <si>
     <t>Dim.LocationProvider.StaffIEN</t>
@@ -1555,25 +1555,25 @@
     <t>PractitionerRole.telecom:va-voice-pager.period</t>
   </si>
   <si>
-    <t>PractitionerRole.telecom:va-digital-pager</t>
-  </si>
-  <si>
-    <t>va-digital-pager</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:va-digital-pager.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:va-digital-pager.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:va-digital-pager.system</t>
+    <t>PractitionerRole.telecom:va-data-pager</t>
+  </si>
+  <si>
+    <t>va-data-pager</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:va-data-pager.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:va-data-pager.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:va-data-pager.system</t>
   </si>
   <si>
     <t>390-1: fixed value = #pager</t>
   </si>
   <si>
-    <t>PractitionerRole.telecom:va-digital-pager.value</t>
+    <t>PractitionerRole.telecom:va-data-pager.value</t>
   </si>
   <si>
     <t>390: source value from NEW PERSON - DIGITAL PAGER (200-.138)</t>
@@ -1582,28 +1582,28 @@
     <t>SStaff.PrescribingProvider.DigitalPager,SStaff.SStaff.DigitalPager</t>
   </si>
   <si>
-    <t>PractitionerRole.telecom:va-digital-pager.use</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:va-digital-pager.rank</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:va-digital-pager.period</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:va-email</t>
-  </si>
-  <si>
-    <t>va-email</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:va-email.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:va-email.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:va-email.system</t>
+    <t>PractitionerRole.telecom:va-data-pager.use</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:va-data-pager.rank</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:va-data-pager.period</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:va-mail</t>
+  </si>
+  <si>
+    <t>va-mail</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:va-mail.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:va-mail.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:va-mail.system</t>
   </si>
   <si>
     <t>email</t>
@@ -1612,7 +1612,7 @@
     <t>391-1: fixed value = #email</t>
   </si>
   <si>
-    <t>PractitionerRole.telecom:va-email.value</t>
+    <t>PractitionerRole.telecom:va-mail.value</t>
   </si>
   <si>
     <t>391: source value from NEW PERSON - EMAIL ADDRESS (200-.151)</t>
@@ -1621,13 +1621,13 @@
     <t>SStaff.PrescribingProvider.EmailAddress,SStaff.SStaff.EmailAddress</t>
   </si>
   <si>
-    <t>PractitionerRole.telecom:va-email.use</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:va-email.rank</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:va-email.period</t>
+    <t>PractitionerRole.telecom:va-mail.use</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:va-mail.rank</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:va-mail.period</t>
   </si>
   <si>
     <t>PractitionerRole.availableTime</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -831,7 +831,7 @@
     <t>PractitionerRole.practitioner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>
@@ -857,7 +857,7 @@
     <t>PractitionerRole.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization)
 </t>
   </si>
   <si>
@@ -1110,7 +1110,7 @@
     <t>PractitionerRole.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Location)
 </t>
   </si>
   <si>
@@ -2111,7 +2111,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="72.5234375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="57.73046875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file NEW PERSON (200) to us-core-practitionerrole</t>
+    <t>This StructureDefinition contains the maps for VistA file HOSPITAL LOCATION (44.1) to us-core-practitionerrole</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1092,7 +1092,7 @@
     <t>PractitionerRole.specialty.coding.code</t>
   </si>
   <si>
-    <t>419: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - X12 CODE (200-8932.1 &gt; 200.05-.01 &gt; 8932.1-6)</t>
+    <t>419: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Person Class &gt; PERSON CLASS - X12 CODE (200-8932.1 &gt; 200.05-.01 &gt; 8932.1-6)</t>
   </si>
   <si>
     <t>PractitionerRole.specialty.coding.display</t>
@@ -1120,7 +1120,7 @@
     <t>The location(s) at which this practitioner provides care.</t>
   </si>
   <si>
-    <t>422: reference from HOSPITAL LOCATION - PROVIDER (44.1-.01)</t>
+    <t>422: reference from HOSPITAL LOCATION - PROVIDER (44.1-.01) case 44-2600=44.1-.01</t>
   </si>
   <si>
     <t>Dim.LocationProvider.StaffIEN</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file HOSPITAL LOCATION (44.1) to us-core-practitionerrole</t>
+    <t>This StructureDefinition contains the maps for VistA file NEW PERSON (200) to us-core-practitionerrole</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$148</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5426" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5653" uniqueCount="602">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1120,10 +1120,10 @@
     <t>The location(s) at which this practitioner provides care.</t>
   </si>
   <si>
-    <t>422: reference from HOSPITAL LOCATION - PROVIDER (44.1-.01) case 44-2600=44.1-.01</t>
-  </si>
-  <si>
-    <t>Dim.LocationProvider.StaffIEN</t>
+    <t>422: reference from HOSPITAL LOCATION - NAME (44-.01) case 44-2600&gt;44.1-.01&gt;200-.01</t>
+  </si>
+  <si>
+    <t>Dim.Location.LocationName,Dim.Location.LocationName</t>
   </si>
   <si>
     <t>.performance.ActDefinitionOrEvent.ServiceDeliveryLocation[@classCode = 'SDLOC']</t>
@@ -1133,6 +1133,95 @@
   </si>
   <si>
     <t>FiveWs.where[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.location.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.location.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.location.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>PractitionerRole.location.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>PractitionerRole.location.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>PractitionerRole.location.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
+  </si>
+  <si>
+    <t>1973: fixed value = - when HOSPITAL LOCATION - PROVIDER &gt; PROVIDER - PROVIDER &gt; NEW PERSON - NAME (44-2600 &gt; 44.1-.01&gt;200-.01)</t>
   </si>
   <si>
     <t>PractitionerRole.healthcareService</t>
@@ -2098,7 +2187,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP142"/>
+  <dimension ref="A1:AP148"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="61.890625" customWidth="true" bestFit="true"/>
@@ -8524,7 +8613,7 @@
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>78</v>
@@ -8536,13 +8625,13 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>363</v>
+        <v>176</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>364</v>
+        <v>148</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>365</v>
+        <v>149</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8593,19 +8682,19 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>362</v>
+        <v>150</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>265</v>
+        <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>78</v>
@@ -8614,10 +8703,10 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>366</v>
+        <v>78</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>367</v>
+        <v>152</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8628,14 +8717,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8645,27 +8734,27 @@
         <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>369</v>
+        <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>370</v>
+        <v>180</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8701,9 +8790,11 @@
         <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AC55" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="AD55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8711,7 +8802,7 @@
         <v>138</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>368</v>
+        <v>156</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8720,10 +8811,10 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>78</v>
@@ -8735,7 +8826,7 @@
         <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>375</v>
+        <v>152</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -8746,10 +8837,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8769,18 +8860,20 @@
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>176</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>148</v>
+        <v>365</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8829,7 +8922,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>150</v>
+        <v>368</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8838,10 +8931,10 @@
         <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>78</v>
+        <v>369</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>78</v>
@@ -8853,7 +8946,7 @@
         <v>78</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>78</v>
@@ -8864,21 +8957,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>78</v>
@@ -8887,19 +8980,19 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>180</v>
+        <v>371</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>181</v>
+        <v>372</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>182</v>
+        <v>373</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8925,43 +9018,43 @@
         <v>78</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>78</v>
+        <v>280</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>78</v>
+        <v>374</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>78</v>
+        <v>375</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>156</v>
+        <v>376</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>78</v>
@@ -8973,7 +9066,7 @@
         <v>78</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -8984,10 +9077,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8995,13 +9088,13 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>78</v>
@@ -9010,15 +9103,17 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>109</v>
+        <v>210</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -9043,32 +9138,32 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="Y58" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>384</v>
-      </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
@@ -9076,7 +9171,7 @@
         <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>101</v>
@@ -9088,13 +9183,13 @@
         <v>78</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>388</v>
+        <v>78</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>78</v>
@@ -9102,10 +9197,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9113,7 +9208,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>89</v>
@@ -9131,17 +9226,15 @@
         <v>176</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9150,7 +9243,7 @@
         <v>78</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>78</v>
+        <v>387</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>78</v>
@@ -9189,7 +9282,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9204,19 +9297,19 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>395</v>
+        <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>396</v>
+        <v>132</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>397</v>
+        <v>78</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>78</v>
@@ -9224,10 +9317,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9238,32 +9331,28 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>109</v>
+        <v>391</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -9287,13 +9376,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -9311,16 +9400,16 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>101</v>
@@ -9332,13 +9421,13 @@
         <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>408</v>
+        <v>78</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>78</v>
@@ -9346,10 +9435,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9360,10 +9449,10 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>78</v>
@@ -9372,18 +9461,18 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -9419,28 +9508,26 @@
         <v>78</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="AC61" s="2"/>
       <c r="AD61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>101</v>
@@ -9452,10 +9539,10 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>152</v>
+        <v>403</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9466,10 +9553,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9489,16 +9576,16 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>231</v>
+        <v>176</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>416</v>
+        <v>148</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>417</v>
+        <v>149</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9549,7 +9636,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>418</v>
+        <v>150</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9561,7 +9648,7 @@
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
@@ -9570,13 +9657,13 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>419</v>
+        <v>152</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>78</v>
@@ -9584,46 +9671,44 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>369</v>
+        <v>134</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>370</v>
+        <v>180</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
       </c>
@@ -9659,19 +9744,19 @@
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>368</v>
+        <v>156</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9680,10 +9765,10 @@
         <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>78</v>
@@ -9695,7 +9780,7 @@
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>375</v>
+        <v>152</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9706,10 +9791,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9717,28 +9802,28 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>148</v>
+        <v>407</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>149</v>
+        <v>408</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9765,13 +9850,13 @@
         <v>78</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>78</v>
+        <v>411</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>78</v>
@@ -9789,7 +9874,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>150</v>
+        <v>412</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9798,10 +9883,10 @@
         <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
@@ -9810,13 +9895,13 @@
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>78</v>
@@ -9824,44 +9909,46 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>377</v>
+        <v>417</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>180</v>
+        <v>418</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>181</v>
+        <v>419</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9897,31 +9984,31 @@
         <v>78</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>156</v>
+        <v>422</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
@@ -9930,13 +10017,13 @@
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>78</v>
+        <v>423</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>152</v>
+        <v>424</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>78</v>
@@ -9944,10 +10031,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9955,16 +10042,16 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I66" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>90</v>
@@ -9973,13 +10060,17 @@
         <v>109</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9988,7 +10079,7 @@
         <v>78</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>426</v>
+        <v>78</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>78</v>
@@ -10003,13 +10094,13 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>382</v>
+        <v>431</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>383</v>
+        <v>432</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -10027,7 +10118,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>384</v>
+        <v>433</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10036,25 +10127,25 @@
         <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>427</v>
+        <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>78</v>
@@ -10062,10 +10153,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>389</v>
+        <v>437</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10073,13 +10164,13 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>78</v>
@@ -10088,20 +10179,18 @@
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>176</v>
+        <v>438</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>78</v>
       </c>
@@ -10149,7 +10238,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>394</v>
+        <v>442</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10164,19 +10253,19 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>429</v>
+        <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>430</v>
+        <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>395</v>
+        <v>152</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>396</v>
+        <v>152</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>397</v>
+        <v>78</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>78</v>
@@ -10184,10 +10273,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>398</v>
+        <v>443</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10201,29 +10290,25 @@
         <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>109</v>
+        <v>231</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>399</v>
+        <v>444</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
       </c>
@@ -10232,7 +10317,7 @@
         <v>78</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>432</v>
+        <v>78</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>78</v>
@@ -10247,13 +10332,13 @@
         <v>78</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -10271,7 +10356,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10286,19 +10371,19 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>433</v>
+        <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>406</v>
+        <v>132</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>408</v>
+        <v>448</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>78</v>
@@ -10306,12 +10391,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="D69" t="s" s="2">
         <v>78</v>
       </c>
@@ -10323,7 +10410,7 @@
         <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>78</v>
@@ -10332,18 +10419,18 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -10391,16 +10478,16 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>101</v>
@@ -10412,10 +10499,10 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>152</v>
+        <v>403</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -10426,10 +10513,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10449,16 +10536,16 @@
         <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>231</v>
+        <v>176</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>416</v>
+        <v>148</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>417</v>
+        <v>149</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10509,7 +10596,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>418</v>
+        <v>150</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10521,7 +10608,7 @@
         <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
@@ -10530,13 +10617,13 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>419</v>
+        <v>152</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>78</v>
@@ -10544,46 +10631,44 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>369</v>
+        <v>134</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>370</v>
+        <v>180</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10619,19 +10704,19 @@
         <v>78</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>368</v>
+        <v>156</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10640,10 +10725,10 @@
         <v>80</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>78</v>
@@ -10655,7 +10740,7 @@
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>375</v>
+        <v>152</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10666,10 +10751,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10677,28 +10762,28 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>148</v>
+        <v>407</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>149</v>
+        <v>408</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10710,7 +10795,7 @@
         <v>78</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>78</v>
+        <v>454</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>78</v>
@@ -10725,13 +10810,13 @@
         <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>78</v>
+        <v>411</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -10749,7 +10834,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>150</v>
+        <v>412</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10758,25 +10843,25 @@
         <v>89</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>78</v>
@@ -10784,44 +10869,46 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>377</v>
+        <v>417</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>180</v>
+        <v>418</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>181</v>
+        <v>419</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10857,46 +10944,46 @@
         <v>78</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>156</v>
+        <v>422</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>78</v>
+        <v>458</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>78</v>
+        <v>423</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>152</v>
+        <v>424</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>78</v>
@@ -10904,10 +10991,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10915,7 +11002,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>89</v>
@@ -10924,7 +11011,7 @@
         <v>90</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>90</v>
@@ -10933,13 +11020,17 @@
         <v>109</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10948,7 +11039,7 @@
         <v>78</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>426</v>
+        <v>460</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>78</v>
@@ -10963,13 +11054,13 @@
         <v>78</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>382</v>
+        <v>431</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>383</v>
+        <v>432</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>78</v>
@@ -10987,7 +11078,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>384</v>
+        <v>433</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10996,25 +11087,25 @@
         <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>78</v>
@@ -11022,10 +11113,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>389</v>
+        <v>437</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11033,13 +11124,13 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>78</v>
@@ -11048,20 +11139,18 @@
         <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>176</v>
+        <v>438</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>78</v>
       </c>
@@ -11109,7 +11198,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>394</v>
+        <v>442</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11124,19 +11213,19 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>443</v>
+        <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>444</v>
+        <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>395</v>
+        <v>152</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>396</v>
+        <v>152</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>397</v>
+        <v>78</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>78</v>
@@ -11144,10 +11233,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>398</v>
+        <v>443</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11164,26 +11253,22 @@
         <v>78</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J76" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>109</v>
+        <v>231</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>399</v>
+        <v>444</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
       </c>
@@ -11207,13 +11292,13 @@
         <v>78</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>78</v>
@@ -11231,7 +11316,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11252,13 +11337,13 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>406</v>
+        <v>132</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>408</v>
+        <v>448</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>78</v>
@@ -11266,12 +11351,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="D77" t="s" s="2">
         <v>78</v>
       </c>
@@ -11283,7 +11370,7 @@
         <v>89</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>78</v>
@@ -11292,18 +11379,18 @@
         <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
       </c>
@@ -11351,16 +11438,16 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>101</v>
@@ -11372,10 +11459,10 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>152</v>
+        <v>403</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>78</v>
@@ -11386,10 +11473,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11409,16 +11496,16 @@
         <v>78</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>231</v>
+        <v>176</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>416</v>
+        <v>148</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>417</v>
+        <v>149</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11469,7 +11556,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>418</v>
+        <v>150</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11481,7 +11568,7 @@
         <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
@@ -11490,13 +11577,13 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>419</v>
+        <v>152</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>78</v>
@@ -11504,46 +11591,44 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>369</v>
+        <v>134</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>370</v>
+        <v>180</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>78</v>
       </c>
@@ -11579,19 +11664,19 @@
         <v>78</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>368</v>
+        <v>156</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11600,10 +11685,10 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
@@ -11615,7 +11700,7 @@
         <v>78</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>375</v>
+        <v>152</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>78</v>
@@ -11626,10 +11711,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11637,28 +11722,28 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>148</v>
+        <v>407</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>149</v>
+        <v>408</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11670,7 +11755,7 @@
         <v>78</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>78</v>
+        <v>454</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>78</v>
@@ -11685,13 +11770,13 @@
         <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>78</v>
+        <v>411</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11709,7 +11794,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>150</v>
+        <v>412</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11718,25 +11803,25 @@
         <v>89</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>78</v>
+        <v>469</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>78</v>
@@ -11744,44 +11829,46 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>377</v>
+        <v>417</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>180</v>
+        <v>418</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>181</v>
+        <v>419</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
       </c>
@@ -11817,46 +11904,46 @@
         <v>78</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>156</v>
+        <v>422</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>78</v>
+        <v>471</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>78</v>
+        <v>472</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>78</v>
+        <v>423</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>152</v>
+        <v>424</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>78</v>
@@ -11864,10 +11951,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11875,16 +11962,16 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I82" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>90</v>
@@ -11893,13 +11980,17 @@
         <v>109</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
       </c>
@@ -11908,7 +11999,7 @@
         <v>78</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>426</v>
+        <v>78</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>78</v>
@@ -11923,13 +12014,13 @@
         <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>382</v>
+        <v>431</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>383</v>
+        <v>432</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11947,7 +12038,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>384</v>
+        <v>433</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11956,25 +12047,25 @@
         <v>89</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>453</v>
+        <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>78</v>
@@ -11982,10 +12073,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>389</v>
+        <v>437</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11993,13 +12084,13 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>78</v>
@@ -12008,20 +12099,18 @@
         <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>176</v>
+        <v>438</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>78</v>
       </c>
@@ -12069,7 +12158,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>394</v>
+        <v>442</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12084,19 +12173,19 @@
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>455</v>
+        <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>395</v>
+        <v>152</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>396</v>
+        <v>152</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>397</v>
+        <v>78</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>78</v>
@@ -12104,10 +12193,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>398</v>
+        <v>443</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12124,26 +12213,22 @@
         <v>78</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J84" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>109</v>
+        <v>231</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>399</v>
+        <v>444</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>78</v>
       </c>
@@ -12167,13 +12252,13 @@
         <v>78</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
@@ -12191,7 +12276,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12212,13 +12297,13 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>406</v>
+        <v>132</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>408</v>
+        <v>448</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>78</v>
@@ -12226,12 +12311,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C85" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="D85" t="s" s="2">
         <v>78</v>
       </c>
@@ -12243,7 +12330,7 @@
         <v>89</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>78</v>
@@ -12252,18 +12339,18 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>78</v>
       </c>
@@ -12311,16 +12398,16 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>101</v>
@@ -12332,10 +12419,10 @@
         <v>78</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>152</v>
+        <v>403</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>78</v>
@@ -12346,10 +12433,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12369,16 +12456,16 @@
         <v>78</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>231</v>
+        <v>176</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>416</v>
+        <v>148</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>417</v>
+        <v>149</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12429,7 +12516,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>418</v>
+        <v>150</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12441,7 +12528,7 @@
         <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
@@ -12450,13 +12537,13 @@
         <v>78</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>419</v>
+        <v>152</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>78</v>
@@ -12464,46 +12551,44 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C87" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>369</v>
+        <v>134</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>370</v>
+        <v>180</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12539,19 +12624,19 @@
         <v>78</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>368</v>
+        <v>156</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12560,10 +12645,10 @@
         <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>78</v>
@@ -12575,7 +12660,7 @@
         <v>78</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>375</v>
+        <v>152</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>78</v>
@@ -12586,10 +12671,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12597,28 +12682,28 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>148</v>
+        <v>407</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>149</v>
+        <v>408</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12630,7 +12715,7 @@
         <v>78</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>78</v>
+        <v>454</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>78</v>
@@ -12645,13 +12730,13 @@
         <v>78</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>78</v>
+        <v>411</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>78</v>
@@ -12669,7 +12754,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>150</v>
+        <v>412</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12678,25 +12763,25 @@
         <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>78</v>
+        <v>481</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>78</v>
@@ -12704,44 +12789,46 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>377</v>
+        <v>417</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>180</v>
+        <v>418</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>181</v>
+        <v>419</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>78</v>
       </c>
@@ -12777,46 +12864,46 @@
         <v>78</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>156</v>
+        <v>422</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>78</v>
+        <v>483</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>78</v>
+        <v>484</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>78</v>
+        <v>423</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>152</v>
+        <v>424</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>78</v>
@@ -12824,10 +12911,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12835,16 +12922,16 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I90" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>90</v>
@@ -12853,13 +12940,17 @@
         <v>109</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
@@ -12868,7 +12959,7 @@
         <v>78</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>426</v>
+        <v>78</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>78</v>
@@ -12883,13 +12974,13 @@
         <v>78</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>382</v>
+        <v>431</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>383</v>
+        <v>432</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>78</v>
@@ -12907,7 +12998,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>384</v>
+        <v>433</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12916,25 +13007,25 @@
         <v>89</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>465</v>
+        <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>78</v>
@@ -12942,10 +13033,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>389</v>
+        <v>437</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12953,13 +13044,13 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>78</v>
@@ -12968,20 +13059,18 @@
         <v>90</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>176</v>
+        <v>438</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>78</v>
       </c>
@@ -13029,7 +13118,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>394</v>
+        <v>442</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13044,19 +13133,19 @@
         <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>467</v>
+        <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>468</v>
+        <v>78</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>395</v>
+        <v>152</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>396</v>
+        <v>152</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>397</v>
+        <v>78</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>78</v>
@@ -13064,10 +13153,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>398</v>
+        <v>443</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13081,29 +13170,25 @@
         <v>89</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J92" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>109</v>
+        <v>231</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>399</v>
+        <v>444</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>78</v>
       </c>
@@ -13112,7 +13197,7 @@
         <v>78</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>432</v>
+        <v>78</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>78</v>
@@ -13127,13 +13212,13 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -13151,7 +13236,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13166,19 +13251,19 @@
         <v>101</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>470</v>
+        <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>406</v>
+        <v>132</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>408</v>
+        <v>448</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>78</v>
@@ -13186,12 +13271,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C93" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="C93" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="D93" t="s" s="2">
         <v>78</v>
       </c>
@@ -13203,7 +13290,7 @@
         <v>89</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>78</v>
@@ -13212,18 +13299,18 @@
         <v>90</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
       </c>
@@ -13271,16 +13358,16 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>101</v>
@@ -13292,10 +13379,10 @@
         <v>78</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>152</v>
+        <v>403</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>78</v>
@@ -13306,10 +13393,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13329,16 +13416,16 @@
         <v>78</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>231</v>
+        <v>176</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>416</v>
+        <v>148</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>417</v>
+        <v>149</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13389,7 +13476,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>418</v>
+        <v>150</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13401,7 +13488,7 @@
         <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>78</v>
@@ -13410,13 +13497,13 @@
         <v>78</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>419</v>
+        <v>152</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>78</v>
@@ -13424,46 +13511,44 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>369</v>
+        <v>134</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>370</v>
+        <v>180</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>78</v>
       </c>
@@ -13499,19 +13584,19 @@
         <v>78</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>368</v>
+        <v>156</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13520,10 +13605,10 @@
         <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>78</v>
@@ -13535,7 +13620,7 @@
         <v>78</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>375</v>
+        <v>152</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>78</v>
@@ -13546,10 +13631,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13557,28 +13642,28 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>148</v>
+        <v>407</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>149</v>
+        <v>408</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13590,7 +13675,7 @@
         <v>78</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>78</v>
+        <v>454</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>78</v>
@@ -13605,13 +13690,13 @@
         <v>78</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>78</v>
+        <v>411</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>78</v>
@@ -13629,7 +13714,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>150</v>
+        <v>412</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13638,25 +13723,25 @@
         <v>89</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>78</v>
+        <v>493</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>78</v>
@@ -13664,44 +13749,46 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>377</v>
+        <v>417</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>180</v>
+        <v>418</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>181</v>
+        <v>419</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
       </c>
@@ -13737,46 +13824,46 @@
         <v>78</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>156</v>
+        <v>422</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>78</v>
+        <v>495</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>78</v>
+        <v>496</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>78</v>
+        <v>423</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>152</v>
+        <v>424</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>78</v>
@@ -13784,10 +13871,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13795,7 +13882,7 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>89</v>
@@ -13804,7 +13891,7 @@
         <v>90</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J98" t="s" s="2">
         <v>90</v>
@@ -13813,13 +13900,17 @@
         <v>109</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>78</v>
       </c>
@@ -13828,7 +13919,7 @@
         <v>78</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>78</v>
@@ -13843,13 +13934,13 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>382</v>
+        <v>431</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>383</v>
+        <v>432</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
@@ -13867,7 +13958,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>384</v>
+        <v>433</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13876,25 +13967,25 @@
         <v>89</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>78</v>
@@ -13902,10 +13993,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>389</v>
+        <v>437</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13913,13 +14004,13 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>78</v>
@@ -13928,20 +14019,18 @@
         <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>176</v>
+        <v>438</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>78</v>
       </c>
@@ -13989,7 +14078,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>394</v>
+        <v>442</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14004,19 +14093,19 @@
         <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>481</v>
+        <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>482</v>
+        <v>78</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>395</v>
+        <v>152</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>396</v>
+        <v>152</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>397</v>
+        <v>78</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>78</v>
@@ -14024,10 +14113,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>398</v>
+        <v>443</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14041,29 +14130,25 @@
         <v>89</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>109</v>
+        <v>231</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>399</v>
+        <v>444</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>78</v>
       </c>
@@ -14072,7 +14157,7 @@
         <v>78</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>432</v>
+        <v>78</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>78</v>
@@ -14087,13 +14172,13 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -14111,7 +14196,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14126,19 +14211,19 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>484</v>
+        <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>406</v>
+        <v>132</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>408</v>
+        <v>448</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>78</v>
@@ -14146,12 +14231,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C101" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="D101" t="s" s="2">
         <v>78</v>
       </c>
@@ -14163,7 +14250,7 @@
         <v>89</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>78</v>
@@ -14172,18 +14259,18 @@
         <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
       </c>
@@ -14231,16 +14318,16 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>101</v>
@@ -14252,10 +14339,10 @@
         <v>78</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>152</v>
+        <v>403</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>78</v>
@@ -14266,10 +14353,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14289,16 +14376,16 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>231</v>
+        <v>176</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>416</v>
+        <v>148</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>417</v>
+        <v>149</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14349,7 +14436,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>418</v>
+        <v>150</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14361,7 +14448,7 @@
         <v>78</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>78</v>
@@ -14370,13 +14457,13 @@
         <v>78</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>419</v>
+        <v>152</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>78</v>
@@ -14384,46 +14471,44 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>369</v>
+        <v>134</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>370</v>
+        <v>180</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>78</v>
       </c>
@@ -14459,19 +14544,19 @@
         <v>78</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>368</v>
+        <v>156</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14480,10 +14565,10 @@
         <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
@@ -14495,7 +14580,7 @@
         <v>78</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>375</v>
+        <v>152</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>78</v>
@@ -14506,10 +14591,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14517,28 +14602,28 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>148</v>
+        <v>407</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>149</v>
+        <v>408</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14550,7 +14635,7 @@
         <v>78</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>78</v>
+        <v>506</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>78</v>
@@ -14565,13 +14650,13 @@
         <v>78</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>78</v>
+        <v>411</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>78</v>
@@ -14589,7 +14674,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>150</v>
+        <v>412</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14598,25 +14683,25 @@
         <v>89</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>78</v>
+        <v>507</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>78</v>
@@ -14624,44 +14709,46 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>377</v>
+        <v>417</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>180</v>
+        <v>418</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>181</v>
+        <v>419</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
       </c>
@@ -14697,46 +14784,46 @@
         <v>78</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>156</v>
+        <v>422</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>78</v>
+        <v>509</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>78</v>
+        <v>510</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>78</v>
+        <v>423</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>152</v>
+        <v>424</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>78</v>
@@ -14744,10 +14831,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14755,7 +14842,7 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>89</v>
@@ -14764,7 +14851,7 @@
         <v>90</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>90</v>
@@ -14773,13 +14860,17 @@
         <v>109</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>78</v>
       </c>
@@ -14788,7 +14879,7 @@
         <v>78</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>78</v>
@@ -14803,13 +14894,13 @@
         <v>78</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>382</v>
+        <v>431</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>383</v>
+        <v>432</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>78</v>
@@ -14827,7 +14918,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>384</v>
+        <v>433</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14836,25 +14927,25 @@
         <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>78</v>
@@ -14862,10 +14953,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>389</v>
+        <v>437</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14873,13 +14964,13 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>78</v>
@@ -14888,20 +14979,18 @@
         <v>90</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>176</v>
+        <v>438</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>78</v>
       </c>
@@ -14949,7 +15038,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>394</v>
+        <v>442</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14964,19 +15053,19 @@
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>495</v>
+        <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>496</v>
+        <v>78</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>395</v>
+        <v>152</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>396</v>
+        <v>152</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>397</v>
+        <v>78</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>78</v>
@@ -14984,10 +15073,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>398</v>
+        <v>443</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15004,26 +15093,22 @@
         <v>78</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J108" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>109</v>
+        <v>231</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>399</v>
+        <v>444</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>78</v>
       </c>
@@ -15047,13 +15132,13 @@
         <v>78</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>78</v>
@@ -15071,7 +15156,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15092,13 +15177,13 @@
         <v>78</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>406</v>
+        <v>132</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>408</v>
+        <v>448</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>78</v>
@@ -15106,12 +15191,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C109" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="D109" t="s" s="2">
         <v>78</v>
       </c>
@@ -15123,7 +15210,7 @@
         <v>89</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>78</v>
@@ -15132,18 +15219,18 @@
         <v>90</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O109" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>78</v>
       </c>
@@ -15191,16 +15278,16 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>101</v>
@@ -15212,10 +15299,10 @@
         <v>78</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>152</v>
+        <v>403</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>78</v>
@@ -15226,10 +15313,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15249,16 +15336,16 @@
         <v>78</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>231</v>
+        <v>176</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>416</v>
+        <v>148</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>417</v>
+        <v>149</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15309,7 +15396,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>418</v>
+        <v>150</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15321,7 +15408,7 @@
         <v>78</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>78</v>
@@ -15330,13 +15417,13 @@
         <v>78</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>419</v>
+        <v>152</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>78</v>
@@ -15344,46 +15431,44 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>369</v>
+        <v>134</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>370</v>
+        <v>180</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>78</v>
       </c>
@@ -15419,19 +15504,19 @@
         <v>78</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>368</v>
+        <v>156</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15440,10 +15525,10 @@
         <v>80</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>78</v>
@@ -15455,7 +15540,7 @@
         <v>78</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>375</v>
+        <v>152</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>78</v>
@@ -15466,10 +15551,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15477,28 +15562,28 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>148</v>
+        <v>407</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>149</v>
+        <v>408</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15510,7 +15595,7 @@
         <v>78</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>78</v>
+        <v>520</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>78</v>
@@ -15525,13 +15610,13 @@
         <v>78</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>78</v>
+        <v>411</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>78</v>
@@ -15549,7 +15634,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>150</v>
+        <v>412</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15558,25 +15643,25 @@
         <v>89</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>78</v>
+        <v>521</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>78</v>
@@ -15584,44 +15669,46 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>377</v>
+        <v>417</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>180</v>
+        <v>418</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>181</v>
+        <v>419</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O113" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
       </c>
@@ -15657,46 +15744,46 @@
         <v>78</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>156</v>
+        <v>422</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>78</v>
+        <v>523</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>78</v>
+        <v>524</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>78</v>
+        <v>423</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>152</v>
+        <v>424</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>78</v>
@@ -15704,10 +15791,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15715,16 +15802,16 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I114" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="J114" t="s" s="2">
         <v>90</v>
@@ -15733,13 +15820,17 @@
         <v>109</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
       </c>
@@ -15748,7 +15839,7 @@
         <v>78</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>492</v>
+        <v>78</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>78</v>
@@ -15763,13 +15854,13 @@
         <v>78</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>382</v>
+        <v>431</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>383</v>
+        <v>432</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>78</v>
@@ -15787,7 +15878,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>384</v>
+        <v>433</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15796,25 +15887,25 @@
         <v>89</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>78</v>
@@ -15822,10 +15913,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>389</v>
+        <v>437</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15833,13 +15924,13 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>78</v>
@@ -15848,20 +15939,18 @@
         <v>90</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>176</v>
+        <v>438</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>78</v>
       </c>
@@ -15909,7 +15998,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>394</v>
+        <v>442</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -15924,19 +16013,19 @@
         <v>101</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>507</v>
+        <v>78</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>508</v>
+        <v>78</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>395</v>
+        <v>152</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>396</v>
+        <v>152</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>397</v>
+        <v>78</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>78</v>
@@ -15944,10 +16033,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>509</v>
+        <v>527</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>398</v>
+        <v>443</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15964,26 +16053,22 @@
         <v>78</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J116" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>109</v>
+        <v>231</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>399</v>
+        <v>444</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>78</v>
       </c>
@@ -16007,13 +16092,13 @@
         <v>78</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>78</v>
@@ -16031,7 +16116,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16052,13 +16137,13 @@
         <v>78</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>406</v>
+        <v>132</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>408</v>
+        <v>448</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>78</v>
@@ -16066,12 +16151,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C117" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="D117" t="s" s="2">
         <v>78</v>
       </c>
@@ -16083,7 +16170,7 @@
         <v>89</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>78</v>
@@ -16092,18 +16179,18 @@
         <v>90</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O117" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>78</v>
       </c>
@@ -16151,16 +16238,16 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>101</v>
@@ -16172,10 +16259,10 @@
         <v>78</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>152</v>
+        <v>403</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>78</v>
@@ -16186,10 +16273,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16209,16 +16296,16 @@
         <v>78</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>231</v>
+        <v>176</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>416</v>
+        <v>148</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>417</v>
+        <v>149</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16269,7 +16356,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>418</v>
+        <v>150</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16281,7 +16368,7 @@
         <v>78</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>78</v>
@@ -16290,13 +16377,13 @@
         <v>78</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>419</v>
+        <v>152</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AP118" t="s" s="2">
         <v>78</v>
@@ -16304,46 +16391,44 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>369</v>
+        <v>134</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>370</v>
+        <v>180</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>78</v>
       </c>
@@ -16379,19 +16464,19 @@
         <v>78</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>368</v>
+        <v>156</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16400,10 +16485,10 @@
         <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>78</v>
@@ -16415,7 +16500,7 @@
         <v>78</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>375</v>
+        <v>152</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>78</v>
@@ -16426,10 +16511,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16437,28 +16522,28 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>148</v>
+        <v>407</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>149</v>
+        <v>408</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16470,7 +16555,7 @@
         <v>78</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>78</v>
+        <v>520</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>78</v>
@@ -16485,13 +16570,13 @@
         <v>78</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>78</v>
+        <v>411</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>78</v>
@@ -16509,7 +16594,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>150</v>
+        <v>412</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16518,25 +16603,25 @@
         <v>89</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>78</v>
@@ -16544,44 +16629,46 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>377</v>
+        <v>417</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>180</v>
+        <v>418</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>181</v>
+        <v>419</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O121" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>78</v>
       </c>
@@ -16617,46 +16704,46 @@
         <v>78</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>156</v>
+        <v>422</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>78</v>
+        <v>535</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>78</v>
+        <v>536</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>78</v>
+        <v>423</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>152</v>
+        <v>424</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>78</v>
@@ -16664,10 +16751,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16675,16 +16762,16 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I122" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="J122" t="s" s="2">
         <v>90</v>
@@ -16693,13 +16780,17 @@
         <v>109</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
       </c>
@@ -16708,7 +16799,7 @@
         <v>78</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>517</v>
+        <v>78</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>78</v>
@@ -16723,13 +16814,13 @@
         <v>78</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>382</v>
+        <v>431</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>383</v>
+        <v>432</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>78</v>
@@ -16747,7 +16838,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>384</v>
+        <v>433</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16756,25 +16847,25 @@
         <v>89</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>518</v>
+        <v>78</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>78</v>
@@ -16782,10 +16873,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>389</v>
+        <v>437</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16793,13 +16884,13 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G123" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>78</v>
@@ -16808,20 +16899,18 @@
         <v>90</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>176</v>
+        <v>438</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>78</v>
       </c>
@@ -16869,7 +16958,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>394</v>
+        <v>442</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16884,19 +16973,19 @@
         <v>101</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>520</v>
+        <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>521</v>
+        <v>78</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>395</v>
+        <v>152</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>396</v>
+        <v>152</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>397</v>
+        <v>78</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>78</v>
@@ -16904,10 +16993,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>522</v>
+        <v>539</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>398</v>
+        <v>443</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16924,26 +17013,22 @@
         <v>78</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J124" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>109</v>
+        <v>231</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>399</v>
+        <v>444</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>78</v>
       </c>
@@ -16967,13 +17052,13 @@
         <v>78</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>78</v>
@@ -16991,7 +17076,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17012,13 +17097,13 @@
         <v>78</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>406</v>
+        <v>132</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>408</v>
+        <v>448</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>78</v>
@@ -17026,12 +17111,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>523</v>
+        <v>540</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C125" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="C125" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="D125" t="s" s="2">
         <v>78</v>
       </c>
@@ -17043,7 +17130,7 @@
         <v>89</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>78</v>
@@ -17052,18 +17139,18 @@
         <v>90</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O125" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>78</v>
       </c>
@@ -17111,16 +17198,16 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>101</v>
@@ -17132,10 +17219,10 @@
         <v>78</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>152</v>
+        <v>403</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>78</v>
@@ -17146,10 +17233,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17169,16 +17256,16 @@
         <v>78</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>231</v>
+        <v>176</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>416</v>
+        <v>148</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>417</v>
+        <v>149</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17229,7 +17316,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>418</v>
+        <v>150</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17241,7 +17328,7 @@
         <v>78</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>78</v>
@@ -17250,13 +17337,13 @@
         <v>78</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>419</v>
+        <v>152</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AP126" t="s" s="2">
         <v>78</v>
@@ -17264,14 +17351,14 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>525</v>
+        <v>405</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
@@ -17290,16 +17377,16 @@
         <v>78</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>526</v>
+        <v>134</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>527</v>
+        <v>180</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>528</v>
+        <v>181</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>529</v>
+        <v>182</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17337,19 +17424,19 @@
         <v>78</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC127" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AD127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>525</v>
+        <v>156</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17361,7 +17448,7 @@
         <v>78</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>78</v>
@@ -17373,7 +17460,7 @@
         <v>78</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>530</v>
+        <v>152</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>78</v>
@@ -17384,10 +17471,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>531</v>
+        <v>406</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17395,28 +17482,28 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G128" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>148</v>
+        <v>407</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>149</v>
+        <v>408</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17428,7 +17515,7 @@
         <v>78</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>78</v>
+        <v>545</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>78</v>
@@ -17443,13 +17530,13 @@
         <v>78</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>78</v>
+        <v>411</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>78</v>
@@ -17467,7 +17554,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>150</v>
+        <v>412</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17476,25 +17563,25 @@
         <v>89</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>78</v>
+        <v>546</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="AP128" t="s" s="2">
         <v>78</v>
@@ -17502,44 +17589,46 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>532</v>
+        <v>417</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>180</v>
+        <v>418</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>181</v>
+        <v>419</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O129" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>78</v>
       </c>
@@ -17587,34 +17676,34 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>156</v>
+        <v>422</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>78</v>
+        <v>548</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>78</v>
+        <v>549</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>78</v>
+        <v>423</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>152</v>
+        <v>424</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="AP129" t="s" s="2">
         <v>78</v>
@@ -17622,21 +17711,21 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>533</v>
+        <v>550</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>533</v>
+        <v>426</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>78</v>
@@ -17648,19 +17737,19 @@
         <v>90</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>535</v>
+        <v>427</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>536</v>
+        <v>428</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>182</v>
+        <v>429</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>207</v>
+        <v>430</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>78</v>
@@ -17685,13 +17774,13 @@
         <v>78</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>78</v>
+        <v>431</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>78</v>
+        <v>432</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>78</v>
@@ -17709,19 +17798,19 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>537</v>
+        <v>433</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>78</v>
@@ -17730,13 +17819,13 @@
         <v>78</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>78</v>
+        <v>434</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>132</v>
+        <v>435</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>78</v>
+        <v>436</v>
       </c>
       <c r="AP130" t="s" s="2">
         <v>78</v>
@@ -17744,10 +17833,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>538</v>
+        <v>551</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>538</v>
+        <v>437</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17758,7 +17847,7 @@
         <v>79</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>78</v>
@@ -17767,18 +17856,20 @@
         <v>78</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>109</v>
+        <v>438</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>539</v>
+        <v>439</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N131" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>78</v>
@@ -17803,13 +17894,13 @@
         <v>78</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>541</v>
+        <v>78</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>542</v>
+        <v>78</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>78</v>
@@ -17827,13 +17918,13 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>538</v>
+        <v>442</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>78</v>
@@ -17848,10 +17939,10 @@
         <v>78</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>530</v>
+        <v>152</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>78</v>
@@ -17862,10 +17953,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>543</v>
+        <v>443</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17885,16 +17976,16 @@
         <v>78</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>544</v>
+        <v>444</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>545</v>
+        <v>445</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17945,7 +18036,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>543</v>
+        <v>446</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -17966,13 +18057,13 @@
         <v>78</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>530</v>
+        <v>447</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>78</v>
+        <v>448</v>
       </c>
       <c r="AP132" t="s" s="2">
         <v>78</v>
@@ -17980,10 +18071,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17994,7 +18085,7 @@
         <v>79</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>78</v>
@@ -18006,16 +18097,16 @@
         <v>78</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18065,13 +18156,13 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>78</v>
@@ -18089,7 +18180,7 @@
         <v>78</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>530</v>
+        <v>558</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>78</v>
@@ -18100,10 +18191,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18126,17 +18217,15 @@
         <v>78</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>547</v>
+        <v>176</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>552</v>
+        <v>148</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>550</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -18185,7 +18274,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>551</v>
+        <v>150</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18197,7 +18286,7 @@
         <v>78</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>78</v>
@@ -18209,7 +18298,7 @@
         <v>78</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>530</v>
+        <v>152</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>78</v>
@@ -18220,14 +18309,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -18246,15 +18335,17 @@
         <v>78</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>526</v>
+        <v>134</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>555</v>
+        <v>180</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N135" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>78</v>
@@ -18303,7 +18394,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>554</v>
+        <v>156</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18315,7 +18406,7 @@
         <v>78</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>78</v>
@@ -18327,7 +18418,7 @@
         <v>78</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>530</v>
+        <v>152</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>78</v>
@@ -18338,42 +18429,46 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>78</v>
+        <v>562</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I136" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>148</v>
+        <v>563</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N136" s="2"/>
-      <c r="O136" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P136" t="s" s="2">
         <v>78</v>
       </c>
@@ -18421,19 +18516,19 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>150</v>
+        <v>565</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>78</v>
@@ -18445,7 +18540,7 @@
         <v>78</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>78</v>
@@ -18456,14 +18551,14 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -18482,17 +18577,15 @@
         <v>78</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>180</v>
+        <v>567</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>78</v>
@@ -18517,13 +18610,13 @@
         <v>78</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>78</v>
+        <v>569</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>78</v>
+        <v>570</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>78</v>
@@ -18541,7 +18634,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>156</v>
+        <v>566</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18553,7 +18646,7 @@
         <v>78</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>78</v>
@@ -18565,7 +18658,7 @@
         <v>78</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>152</v>
+        <v>558</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>78</v>
@@ -18576,46 +18669,42 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I138" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>134</v>
+        <v>219</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>535</v>
+        <v>572</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>78</v>
       </c>
@@ -18663,19 +18752,19 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>537</v>
+        <v>571</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>78</v>
@@ -18687,7 +18776,7 @@
         <v>78</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>132</v>
+        <v>558</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>78</v>
@@ -18698,10 +18787,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18709,7 +18798,7 @@
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G139" t="s" s="2">
         <v>89</v>
@@ -18724,15 +18813,17 @@
         <v>78</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>176</v>
+        <v>575</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N139" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>78</v>
@@ -18781,10 +18872,10 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>89</v>
@@ -18805,7 +18896,7 @@
         <v>78</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>152</v>
+        <v>558</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>78</v>
@@ -18816,10 +18907,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>563</v>
+        <v>579</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>563</v>
+        <v>579</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18842,15 +18933,17 @@
         <v>78</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>231</v>
+        <v>575</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>564</v>
+        <v>580</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N140" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>78</v>
@@ -18899,7 +18992,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>563</v>
+        <v>579</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18923,7 +19016,7 @@
         <v>78</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>530</v>
+        <v>558</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>78</v>
@@ -18934,10 +19027,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>566</v>
+        <v>582</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>566</v>
+        <v>582</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18948,7 +19041,7 @@
         <v>79</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>78</v>
@@ -18960,13 +19053,13 @@
         <v>78</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>176</v>
+        <v>554</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>568</v>
+        <v>584</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19017,13 +19110,13 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>566</v>
+        <v>582</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>78</v>
@@ -19041,7 +19134,7 @@
         <v>78</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>530</v>
+        <v>558</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>78</v>
@@ -19052,10 +19145,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19066,10 +19159,10 @@
         <v>79</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>78</v>
@@ -19078,18 +19171,16 @@
         <v>78</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>570</v>
+        <v>176</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>571</v>
+        <v>148</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>572</v>
+        <v>149</v>
       </c>
       <c r="N142" s="2"/>
-      <c r="O142" t="s" s="2">
-        <v>573</v>
-      </c>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>78</v>
       </c>
@@ -19137,19 +19228,19 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>569</v>
+        <v>150</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>78</v>
@@ -19170,8 +19261,724 @@
         <v>78</v>
       </c>
     </row>
+    <row r="143" hidden="true">
+      <c r="A143" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O143" s="2"/>
+      <c r="P143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q143" s="2"/>
+      <c r="R143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN143" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AO143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP143" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="144" hidden="true">
+      <c r="A144" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="P144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN144" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AO144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP144" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="145" hidden="true">
+      <c r="A145" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" s="2"/>
+      <c r="P145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AO145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP145" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="146" hidden="true">
+      <c r="A146" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="N146" s="2"/>
+      <c r="O146" s="2"/>
+      <c r="P146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AO146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP146" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="147" hidden="true">
+      <c r="A147" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="N147" s="2"/>
+      <c r="O147" s="2"/>
+      <c r="P147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q147" s="2"/>
+      <c r="R147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AO147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP147" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="148" hidden="true">
+      <c r="A148" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N148" s="2"/>
+      <c r="O148" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="P148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q148" s="2"/>
+      <c r="R148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AO148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP148" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AP142">
+  <autoFilter ref="A1:AP148">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -19181,7 +19988,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI141">
+  <conditionalFormatting sqref="A2:AI147">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5426" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5426" uniqueCount="575">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1782,6 +1782,9 @@
     <t>Organizations have multiple systems that provide various services and ,ay also be different for practitioners too.  So the endpoint satisfies the need to be able to define the technical connection details for how to connect to them, and for what purpose.</t>
+  </si>
+  <si>
+    <t>2013: target not supported</t>
   </si>
 </sst>
 </file>
@@ -19152,7 +19155,7 @@
         <v>101</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>78</v>
+        <v>574</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1098,7 +1098,10 @@
     <t>PractitionerRole.specialty.coding.display</t>
   </si>
   <si>
-    <t>419-2: undefined</t>
+    <t>concat({PROVIDER TYPE (.01)}, {CLASSIFICATION (1)}, {AREA OF SPECIALIZATION (2)})</t>
+  </si>
+  <si>
+    <t>419-2: fixed value = concat({PROVIDER TYPE (.01)}, {CLASSIFICATION (1)}, {AREA OF SPECIALIZATION (2)})</t>
   </si>
   <si>
     <t>PractitionerRole.specialty.coding.userSelected</t>
@@ -1110,7 +1113,7 @@
     <t>PractitionerRole.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Location)
 </t>
   </si>
   <si>
@@ -1120,10 +1123,7 @@
     <t>The location(s) at which this practitioner provides care.</t>
   </si>
   <si>
-    <t>422: reference from HOSPITAL LOCATION - PROVIDER (44.1-.01)</t>
-  </si>
-  <si>
-    <t>Dim.LocationProvider.StaffIEN</t>
+    <t>422: reference from HOSPITAL LOCATION - (44-) case 44-2600&gt;44.1-.01&gt;200</t>
   </si>
   <si>
     <t>.performance.ActDefinitionOrEvent.ServiceDeliveryLocation[@classCode = 'SDLOC']</t>
@@ -8077,7 +8077,7 @@
         <v>78</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>78</v>
+        <v>350</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>78</v>
@@ -8131,7 +8131,7 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>78</v>
@@ -8151,10 +8151,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8273,10 +8273,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8395,10 +8395,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8421,13 +8421,13 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8478,7 +8478,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8493,10 +8493,10 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>358</v>
+        <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5426" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5426" uniqueCount="576">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -715,6 +715,10 @@
   </si>
   <si>
     <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+PractitionerRole-411:if date &gt; now or = null then fixed value true {null}PractitionerRole-412:if date &lt; now then fixed value false {null}</t>
   </si>
   <si>
     <t>412: fixed value = false when NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Expiration Date (200-8932.1 &gt; 200.05-3) case date &lt; now</t>
@@ -4650,33 +4654,33 @@
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>225</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4699,17 +4703,17 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -4758,7 +4762,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4779,24 +4783,24 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4911,10 +4915,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5031,10 +5035,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5057,16 +5061,16 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5116,7 +5120,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5125,22 +5129,22 @@
         <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>78</v>
@@ -5151,10 +5155,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5177,23 +5181,23 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="R26" t="s" s="2">
         <v>78</v>
@@ -5238,7 +5242,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5247,22 +5251,22 @@
         <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>78</v>
@@ -5273,10 +5277,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5299,13 +5303,13 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5356,7 +5360,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5365,22 +5369,22 @@
         <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>78</v>
@@ -5391,10 +5395,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5417,13 +5421,13 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5474,7 +5478,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5483,13 +5487,13 @@
         <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>78</v>
@@ -5498,7 +5502,7 @@
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>78</v>
@@ -5509,10 +5513,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5538,16 +5542,16 @@
         <v>166</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -5572,13 +5576,13 @@
         <v>78</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>78</v>
@@ -5596,7 +5600,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5617,13 +5621,13 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>78</v>
@@ -5631,10 +5635,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5749,10 +5753,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5869,10 +5873,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5991,10 +5995,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6109,10 +6113,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6229,10 +6233,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6258,16 +6262,16 @@
         <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -6277,7 +6281,7 @@
         <v>78</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>78</v>
@@ -6316,7 +6320,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6331,16 +6335,16 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>78</v>
@@ -6351,10 +6355,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6380,13 +6384,13 @@
         <v>176</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6436,7 +6440,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6457,10 +6461,10 @@
         <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>78</v>
@@ -6471,10 +6475,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6500,14 +6504,14 @@
         <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6556,7 +6560,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6571,16 +6575,16 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>78</v>
@@ -6591,10 +6595,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6620,14 +6624,14 @@
         <v>176</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6676,7 +6680,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6691,16 +6695,16 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>78</v>
@@ -6711,10 +6715,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6740,16 +6744,16 @@
         <v>219</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6798,7 +6802,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6819,10 +6823,10 @@
         <v>78</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>78</v>
@@ -6833,10 +6837,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6955,10 +6959,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6984,10 +6988,10 @@
         <v>166</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7014,11 +7018,11 @@
         <v>78</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>78</v>
@@ -7036,7 +7040,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7057,13 +7061,13 @@
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>78</v>
@@ -7071,10 +7075,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7189,10 +7193,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7309,10 +7313,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7431,10 +7435,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7549,10 +7553,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7669,10 +7673,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7698,16 +7702,16 @@
         <v>103</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
@@ -7717,7 +7721,7 @@
         <v>78</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>78</v>
@@ -7756,7 +7760,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7771,16 +7775,16 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
@@ -7791,10 +7795,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7820,13 +7824,13 @@
         <v>176</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7876,7 +7880,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7897,10 +7901,10 @@
         <v>78</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>78</v>
@@ -7911,10 +7915,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7940,14 +7944,14 @@
         <v>109</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7996,7 +8000,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8011,16 +8015,16 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
@@ -8031,10 +8035,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8060,14 +8064,14 @@
         <v>176</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -8077,7 +8081,7 @@
         <v>78</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>78</v>
@@ -8116,7 +8120,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8131,16 +8135,16 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
@@ -8151,10 +8155,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8180,16 +8184,16 @@
         <v>219</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -8238,7 +8242,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8259,10 +8263,10 @@
         <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>78</v>
@@ -8273,10 +8277,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8395,10 +8399,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8421,13 +8425,13 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8478,7 +8482,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8487,13 +8491,13 @@
         <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>78</v>
@@ -8502,21 +8506,21 @@
         <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8539,13 +8543,13 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8596,7 +8600,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8605,7 +8609,7 @@
         <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>101</v>
@@ -8617,10 +8621,10 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8631,10 +8635,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8657,17 +8661,17 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8704,7 +8708,7 @@
         <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
@@ -8714,7 +8718,7 @@
         <v>138</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8723,7 +8727,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>101</v>
@@ -8738,7 +8742,7 @@
         <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -8749,10 +8753,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8867,10 +8871,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8987,10 +8991,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9016,10 +9020,10 @@
         <v>109</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9046,13 +9050,13 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -9070,7 +9074,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9079,7 +9083,7 @@
         <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>101</v>
@@ -9091,13 +9095,13 @@
         <v>78</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>78</v>
@@ -9105,10 +9109,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9134,16 +9138,16 @@
         <v>176</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -9192,7 +9196,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9213,13 +9217,13 @@
         <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>78</v>
@@ -9227,10 +9231,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9256,16 +9260,16 @@
         <v>109</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9290,13 +9294,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -9314,7 +9318,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9335,13 +9339,13 @@
         <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>78</v>
@@ -9349,10 +9353,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9375,16 +9379,16 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9434,7 +9438,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9469,10 +9473,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9495,13 +9499,13 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9552,7 +9556,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9576,10 +9580,10 @@
         <v>132</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>78</v>
@@ -9587,13 +9591,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>78</v>
@@ -9615,17 +9619,17 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9674,7 +9678,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9683,7 +9687,7 @@
         <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>101</v>
@@ -9698,7 +9702,7 @@
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9709,10 +9713,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9827,10 +9831,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9947,10 +9951,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9976,10 +9980,10 @@
         <v>109</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9991,7 +9995,7 @@
         <v>78</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>78</v>
@@ -10006,13 +10010,13 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -10030,7 +10034,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10039,25 +10043,25 @@
         <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>78</v>
@@ -10065,10 +10069,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10094,16 +10098,16 @@
         <v>176</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -10152,7 +10156,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10167,19 +10171,19 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>78</v>
@@ -10187,10 +10191,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10216,16 +10220,16 @@
         <v>109</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10235,7 +10239,7 @@
         <v>78</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>78</v>
@@ -10250,13 +10254,13 @@
         <v>78</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -10274,7 +10278,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10289,19 +10293,19 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>78</v>
@@ -10309,10 +10313,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10335,16 +10339,16 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10394,7 +10398,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10429,10 +10433,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10455,13 +10459,13 @@
         <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10512,7 +10516,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10536,10 +10540,10 @@
         <v>132</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>78</v>
@@ -10547,13 +10551,13 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>78</v>
@@ -10575,17 +10579,17 @@
         <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10634,7 +10638,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10643,7 +10647,7 @@
         <v>80</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>101</v>
@@ -10658,7 +10662,7 @@
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10669,10 +10673,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10787,10 +10791,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10907,10 +10911,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10936,10 +10940,10 @@
         <v>109</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10951,7 +10955,7 @@
         <v>78</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>78</v>
@@ -10966,13 +10970,13 @@
         <v>78</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>78</v>
@@ -10990,7 +10994,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10999,25 +11003,25 @@
         <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>78</v>
@@ -11025,10 +11029,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11054,16 +11058,16 @@
         <v>176</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -11112,7 +11116,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11127,19 +11131,19 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>78</v>
@@ -11147,10 +11151,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11176,16 +11180,16 @@
         <v>109</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -11210,13 +11214,13 @@
         <v>78</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>78</v>
@@ -11234,7 +11238,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11255,13 +11259,13 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>78</v>
@@ -11269,10 +11273,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11295,16 +11299,16 @@
         <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11354,7 +11358,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11389,10 +11393,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11415,13 +11419,13 @@
         <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11472,7 +11476,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11496,10 +11500,10 @@
         <v>132</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>78</v>
@@ -11507,13 +11511,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>78</v>
@@ -11535,17 +11539,17 @@
         <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11594,7 +11598,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11603,7 +11607,7 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>101</v>
@@ -11618,7 +11622,7 @@
         <v>78</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>78</v>
@@ -11629,10 +11633,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11747,10 +11751,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11867,10 +11871,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11896,10 +11900,10 @@
         <v>109</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11911,7 +11915,7 @@
         <v>78</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>78</v>
@@ -11926,13 +11930,13 @@
         <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11950,7 +11954,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11959,25 +11963,25 @@
         <v>89</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>78</v>
@@ -11985,10 +11989,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12014,16 +12018,16 @@
         <v>176</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -12072,7 +12076,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12087,19 +12091,19 @@
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>78</v>
@@ -12107,10 +12111,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12136,16 +12140,16 @@
         <v>109</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -12170,13 +12174,13 @@
         <v>78</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
@@ -12194,7 +12198,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12215,13 +12219,13 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>78</v>
@@ -12229,10 +12233,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12255,16 +12259,16 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12314,7 +12318,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12349,10 +12353,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12375,13 +12379,13 @@
         <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12432,7 +12436,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12456,10 +12460,10 @@
         <v>132</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>78</v>
@@ -12467,13 +12471,13 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>78</v>
@@ -12495,17 +12499,17 @@
         <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
@@ -12554,7 +12558,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12563,7 +12567,7 @@
         <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>101</v>
@@ -12578,7 +12582,7 @@
         <v>78</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>78</v>
@@ -12589,10 +12593,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12707,10 +12711,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12827,10 +12831,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12856,10 +12860,10 @@
         <v>109</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12871,7 +12875,7 @@
         <v>78</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>78</v>
@@ -12886,13 +12890,13 @@
         <v>78</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>78</v>
@@ -12910,7 +12914,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12919,25 +12923,25 @@
         <v>89</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>78</v>
@@ -12945,10 +12949,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12974,16 +12978,16 @@
         <v>176</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -13032,7 +13036,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13047,19 +13051,19 @@
         <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>78</v>
@@ -13067,10 +13071,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13096,16 +13100,16 @@
         <v>109</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -13115,7 +13119,7 @@
         <v>78</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>78</v>
@@ -13130,13 +13134,13 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -13154,7 +13158,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13169,19 +13173,19 @@
         <v>101</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>78</v>
@@ -13189,10 +13193,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13215,16 +13219,16 @@
         <v>90</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13274,7 +13278,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13309,10 +13313,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13335,13 +13339,13 @@
         <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13392,7 +13396,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13416,10 +13420,10 @@
         <v>132</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>78</v>
@@ -13427,13 +13431,13 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>78</v>
@@ -13455,17 +13459,17 @@
         <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>78</v>
@@ -13514,7 +13518,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13523,7 +13527,7 @@
         <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>101</v>
@@ -13538,7 +13542,7 @@
         <v>78</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>78</v>
@@ -13549,10 +13553,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13667,10 +13671,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13787,10 +13791,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13816,10 +13820,10 @@
         <v>109</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13831,7 +13835,7 @@
         <v>78</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>78</v>
@@ -13846,13 +13850,13 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
@@ -13870,7 +13874,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13879,25 +13883,25 @@
         <v>89</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>78</v>
@@ -13905,10 +13909,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13934,16 +13938,16 @@
         <v>176</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13992,7 +13996,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14007,19 +14011,19 @@
         <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>78</v>
@@ -14027,10 +14031,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14056,16 +14060,16 @@
         <v>109</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -14075,7 +14079,7 @@
         <v>78</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>78</v>
@@ -14090,13 +14094,13 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -14114,7 +14118,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14129,19 +14133,19 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>78</v>
@@ -14149,10 +14153,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14175,16 +14179,16 @@
         <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14234,7 +14238,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14269,10 +14273,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14295,13 +14299,13 @@
         <v>90</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14352,7 +14356,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14376,10 +14380,10 @@
         <v>132</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>78</v>
@@ -14387,13 +14391,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>78</v>
@@ -14415,17 +14419,17 @@
         <v>90</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14474,7 +14478,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14483,7 +14487,7 @@
         <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>101</v>
@@ -14498,7 +14502,7 @@
         <v>78</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>78</v>
@@ -14509,10 +14513,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14627,10 +14631,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14747,10 +14751,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14776,10 +14780,10 @@
         <v>109</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14791,7 +14795,7 @@
         <v>78</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>78</v>
@@ -14806,13 +14810,13 @@
         <v>78</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>78</v>
@@ -14830,7 +14834,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14839,25 +14843,25 @@
         <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>78</v>
@@ -14865,10 +14869,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14894,16 +14898,16 @@
         <v>176</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -14952,7 +14956,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14967,19 +14971,19 @@
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>78</v>
@@ -14987,10 +14991,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15016,16 +15020,16 @@
         <v>109</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -15050,13 +15054,13 @@
         <v>78</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>78</v>
@@ -15074,7 +15078,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15095,13 +15099,13 @@
         <v>78</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>78</v>
@@ -15109,10 +15113,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15135,16 +15139,16 @@
         <v>90</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15194,7 +15198,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15229,10 +15233,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15255,13 +15259,13 @@
         <v>90</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15312,7 +15316,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15336,10 +15340,10 @@
         <v>132</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>78</v>
@@ -15347,13 +15351,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>78</v>
@@ -15375,17 +15379,17 @@
         <v>90</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -15434,7 +15438,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15443,7 +15447,7 @@
         <v>80</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>101</v>
@@ -15458,7 +15462,7 @@
         <v>78</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>78</v>
@@ -15469,10 +15473,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15587,10 +15591,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15707,10 +15711,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15736,10 +15740,10 @@
         <v>109</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15751,7 +15755,7 @@
         <v>78</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>78</v>
@@ -15766,13 +15770,13 @@
         <v>78</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>78</v>
@@ -15790,7 +15794,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15799,25 +15803,25 @@
         <v>89</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>78</v>
@@ -15825,10 +15829,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15854,16 +15858,16 @@
         <v>176</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>78</v>
@@ -15912,7 +15916,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -15927,19 +15931,19 @@
         <v>101</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>78</v>
@@ -15947,10 +15951,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15976,16 +15980,16 @@
         <v>109</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -16010,13 +16014,13 @@
         <v>78</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>78</v>
@@ -16034,7 +16038,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16055,13 +16059,13 @@
         <v>78</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>78</v>
@@ -16069,10 +16073,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16095,16 +16099,16 @@
         <v>90</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16154,7 +16158,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16189,10 +16193,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16215,13 +16219,13 @@
         <v>90</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16272,7 +16276,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16296,10 +16300,10 @@
         <v>132</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP118" t="s" s="2">
         <v>78</v>
@@ -16307,13 +16311,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>78</v>
@@ -16335,17 +16339,17 @@
         <v>90</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>78</v>
@@ -16394,7 +16398,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16403,7 +16407,7 @@
         <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>101</v>
@@ -16418,7 +16422,7 @@
         <v>78</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>78</v>
@@ -16429,10 +16433,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16547,10 +16551,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16667,10 +16671,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16696,10 +16700,10 @@
         <v>109</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16711,7 +16715,7 @@
         <v>78</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>78</v>
@@ -16726,13 +16730,13 @@
         <v>78</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>78</v>
@@ -16750,7 +16754,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16759,25 +16763,25 @@
         <v>89</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>78</v>
@@ -16785,10 +16789,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16814,16 +16818,16 @@
         <v>176</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16872,7 +16876,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16887,19 +16891,19 @@
         <v>101</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>78</v>
@@ -16907,10 +16911,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16936,16 +16940,16 @@
         <v>109</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -16970,13 +16974,13 @@
         <v>78</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>78</v>
@@ -16994,7 +16998,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17015,13 +17019,13 @@
         <v>78</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>78</v>
@@ -17029,10 +17033,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17055,16 +17059,16 @@
         <v>90</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17114,7 +17118,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17149,10 +17153,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17175,13 +17179,13 @@
         <v>90</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17232,7 +17236,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17256,10 +17260,10 @@
         <v>132</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP126" t="s" s="2">
         <v>78</v>
@@ -17267,10 +17271,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17293,16 +17297,16 @@
         <v>78</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17352,7 +17356,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17376,7 +17380,7 @@
         <v>78</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>78</v>
@@ -17387,10 +17391,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17505,10 +17509,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17625,14 +17629,14 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -17654,10 +17658,10 @@
         <v>134</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>182</v>
@@ -17712,7 +17716,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17747,10 +17751,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17776,10 +17780,10 @@
         <v>109</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17806,13 +17810,13 @@
         <v>78</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>78</v>
@@ -17830,7 +17834,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17854,7 +17858,7 @@
         <v>78</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>78</v>
@@ -17865,10 +17869,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17894,10 +17898,10 @@
         <v>219</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17948,7 +17952,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -17972,7 +17976,7 @@
         <v>78</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>78</v>
@@ -17983,10 +17987,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18009,16 +18013,16 @@
         <v>78</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18068,7 +18072,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18092,7 +18096,7 @@
         <v>78</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>78</v>
@@ -18103,10 +18107,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18129,16 +18133,16 @@
         <v>78</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18188,7 +18192,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18212,7 +18216,7 @@
         <v>78</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>78</v>
@@ -18223,10 +18227,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18249,13 +18253,13 @@
         <v>78</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18306,7 +18310,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18330,7 +18334,7 @@
         <v>78</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>78</v>
@@ -18341,10 +18345,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18459,10 +18463,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18579,14 +18583,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -18608,10 +18612,10 @@
         <v>134</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>182</v>
@@ -18666,7 +18670,7 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -18701,10 +18705,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18730,10 +18734,10 @@
         <v>176</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -18784,7 +18788,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>89</v>
@@ -18819,10 +18823,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18845,13 +18849,13 @@
         <v>78</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18902,7 +18906,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18926,7 +18930,7 @@
         <v>78</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>78</v>
@@ -18937,10 +18941,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18966,10 +18970,10 @@
         <v>176</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19020,7 +19024,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19044,7 +19048,7 @@
         <v>78</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>78</v>
@@ -19055,10 +19059,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19081,17 +19085,17 @@
         <v>78</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
@@ -19140,7 +19144,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19149,13 +19153,13 @@
         <v>80</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -718,7 +718,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-PractitionerRole-411:if date &gt; now or = null then fixed value true {null}PractitionerRole-412:if date &lt; now then fixed value false {null}</t>
+pr-16-411:200-8932.1 &gt; 200.05-3: if date &gt; now or = null then true {null}pr-16-412:200-8932.1 &gt; 200.05-3: if date &lt; now then false {null}</t>
   </si>
   <si>
     <t>412: fixed value = false when NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Expiration Date (200-8932.1 &gt; 200.05-3) case date &lt; now</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file NEW PERSON (200) to us-core-practitionerrole</t>
+    <t>This StructureDefinition contains the maps for VistA file NEW PERSON (200) to us-core-practitionerrole.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5426" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5426" uniqueCount="577">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1127,6 +1127,10 @@
     <t>The location(s) at which this practitioner provides care.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+pr-16-422:44-: if 44-2600&gt;44.1-.01&gt;200 then /Location {null}</t>
+  </si>
+  <si>
     <t>422: reference from HOSPITAL LOCATION - (44-) case 44-2600&gt;44.1-.01&gt;200</t>
   </si>
   <si>
@@ -1174,7 +1178,7 @@
     <t>Often practitioners have a dedicated line for each location (or service) that they work at, and need to be able to define separate contact details for each of these.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>
@@ -8494,10 +8498,10 @@
         <v>266</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>359</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>78</v>
@@ -8506,21 +8510,21 @@
         <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8543,13 +8547,13 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8600,7 +8604,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8621,10 +8625,10 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8635,10 +8639,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8661,17 +8665,17 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8708,7 +8712,7 @@
         <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
@@ -8718,7 +8722,7 @@
         <v>138</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8727,7 +8731,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>101</v>
@@ -8742,7 +8746,7 @@
         <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -8753,10 +8757,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8871,10 +8875,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8991,10 +8995,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9020,10 +9024,10 @@
         <v>109</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9050,13 +9054,13 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -9074,7 +9078,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9083,7 +9087,7 @@
         <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>101</v>
@@ -9095,13 +9099,13 @@
         <v>78</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>78</v>
@@ -9109,10 +9113,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9138,16 +9142,16 @@
         <v>176</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -9196,7 +9200,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9217,13 +9221,13 @@
         <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>78</v>
@@ -9231,10 +9235,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9260,16 +9264,16 @@
         <v>109</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9294,13 +9298,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -9318,7 +9322,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9339,13 +9343,13 @@
         <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>78</v>
@@ -9353,10 +9357,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9379,16 +9383,16 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9438,7 +9442,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9473,10 +9477,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9502,10 +9506,10 @@
         <v>232</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9556,7 +9560,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9580,10 +9584,10 @@
         <v>132</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>78</v>
@@ -9591,13 +9595,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>78</v>
@@ -9619,17 +9623,17 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9678,7 +9682,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9687,7 +9691,7 @@
         <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>101</v>
@@ -9702,7 +9706,7 @@
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9713,10 +9717,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9831,10 +9835,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9951,10 +9955,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9980,10 +9984,10 @@
         <v>109</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9995,7 +9999,7 @@
         <v>78</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>78</v>
@@ -10010,13 +10014,13 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -10034,7 +10038,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10043,25 +10047,25 @@
         <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>78</v>
@@ -10069,10 +10073,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10098,16 +10102,16 @@
         <v>176</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -10156,7 +10160,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10171,19 +10175,19 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>78</v>
@@ -10191,10 +10195,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10220,16 +10224,16 @@
         <v>109</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10239,7 +10243,7 @@
         <v>78</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>78</v>
@@ -10254,13 +10258,13 @@
         <v>78</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -10278,7 +10282,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10293,19 +10297,19 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>78</v>
@@ -10313,10 +10317,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10339,16 +10343,16 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10398,7 +10402,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10433,10 +10437,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10462,10 +10466,10 @@
         <v>232</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10516,7 +10520,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10540,10 +10544,10 @@
         <v>132</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>78</v>
@@ -10551,13 +10555,13 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>78</v>
@@ -10579,17 +10583,17 @@
         <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10638,7 +10642,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10647,7 +10651,7 @@
         <v>80</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>101</v>
@@ -10662,7 +10666,7 @@
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10673,10 +10677,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10791,10 +10795,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10911,10 +10915,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10940,10 +10944,10 @@
         <v>109</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10955,7 +10959,7 @@
         <v>78</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>78</v>
@@ -10970,13 +10974,13 @@
         <v>78</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>78</v>
@@ -10994,7 +10998,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11003,25 +11007,25 @@
         <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>78</v>
@@ -11029,10 +11033,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11058,16 +11062,16 @@
         <v>176</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -11116,7 +11120,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11131,19 +11135,19 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>78</v>
@@ -11151,10 +11155,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11180,16 +11184,16 @@
         <v>109</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -11214,13 +11218,13 @@
         <v>78</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>78</v>
@@ -11238,7 +11242,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11259,13 +11263,13 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>78</v>
@@ -11273,10 +11277,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11299,16 +11303,16 @@
         <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11358,7 +11362,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11393,10 +11397,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11422,10 +11426,10 @@
         <v>232</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11476,7 +11480,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11500,10 +11504,10 @@
         <v>132</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>78</v>
@@ -11511,13 +11515,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>78</v>
@@ -11539,17 +11543,17 @@
         <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11598,7 +11602,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11607,7 +11611,7 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>101</v>
@@ -11622,7 +11626,7 @@
         <v>78</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>78</v>
@@ -11633,10 +11637,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11751,10 +11755,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11871,10 +11875,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11900,10 +11904,10 @@
         <v>109</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11915,7 +11919,7 @@
         <v>78</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>78</v>
@@ -11930,13 +11934,13 @@
         <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11954,7 +11958,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11963,25 +11967,25 @@
         <v>89</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>78</v>
@@ -11989,10 +11993,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12018,16 +12022,16 @@
         <v>176</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -12076,7 +12080,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12091,19 +12095,19 @@
         <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>78</v>
@@ -12111,10 +12115,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12140,16 +12144,16 @@
         <v>109</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -12174,13 +12178,13 @@
         <v>78</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
@@ -12198,7 +12202,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12219,13 +12223,13 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>78</v>
@@ -12233,10 +12237,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12259,16 +12263,16 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12318,7 +12322,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12353,10 +12357,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12382,10 +12386,10 @@
         <v>232</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12436,7 +12440,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12460,10 +12464,10 @@
         <v>132</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>78</v>
@@ -12471,13 +12475,13 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>78</v>
@@ -12499,17 +12503,17 @@
         <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
@@ -12558,7 +12562,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12567,7 +12571,7 @@
         <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>101</v>
@@ -12582,7 +12586,7 @@
         <v>78</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>78</v>
@@ -12593,10 +12597,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12711,10 +12715,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12831,10 +12835,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12860,10 +12864,10 @@
         <v>109</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12875,7 +12879,7 @@
         <v>78</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>78</v>
@@ -12890,13 +12894,13 @@
         <v>78</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>78</v>
@@ -12914,7 +12918,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12923,25 +12927,25 @@
         <v>89</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>78</v>
@@ -12949,10 +12953,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12978,16 +12982,16 @@
         <v>176</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -13036,7 +13040,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13051,19 +13055,19 @@
         <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>78</v>
@@ -13071,10 +13075,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13100,16 +13104,16 @@
         <v>109</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -13119,7 +13123,7 @@
         <v>78</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>78</v>
@@ -13134,13 +13138,13 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -13158,7 +13162,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13173,19 +13177,19 @@
         <v>101</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>78</v>
@@ -13193,10 +13197,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13219,16 +13223,16 @@
         <v>90</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13278,7 +13282,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13313,10 +13317,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13342,10 +13346,10 @@
         <v>232</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13396,7 +13400,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13420,10 +13424,10 @@
         <v>132</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>78</v>
@@ -13431,13 +13435,13 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>78</v>
@@ -13459,17 +13463,17 @@
         <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>78</v>
@@ -13518,7 +13522,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13527,7 +13531,7 @@
         <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>101</v>
@@ -13542,7 +13546,7 @@
         <v>78</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>78</v>
@@ -13553,10 +13557,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13671,10 +13675,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13791,10 +13795,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13820,10 +13824,10 @@
         <v>109</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13835,7 +13839,7 @@
         <v>78</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>78</v>
@@ -13850,13 +13854,13 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
@@ -13874,7 +13878,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13883,25 +13887,25 @@
         <v>89</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>78</v>
@@ -13909,10 +13913,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13938,16 +13942,16 @@
         <v>176</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13996,7 +14000,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14011,19 +14015,19 @@
         <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>78</v>
@@ -14031,10 +14035,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14060,16 +14064,16 @@
         <v>109</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -14079,7 +14083,7 @@
         <v>78</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>78</v>
@@ -14094,13 +14098,13 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -14118,7 +14122,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14133,19 +14137,19 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>78</v>
@@ -14153,10 +14157,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14179,16 +14183,16 @@
         <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14238,7 +14242,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14273,10 +14277,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14302,10 +14306,10 @@
         <v>232</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14356,7 +14360,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14380,10 +14384,10 @@
         <v>132</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>78</v>
@@ -14391,13 +14395,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>78</v>
@@ -14419,17 +14423,17 @@
         <v>90</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14478,7 +14482,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14487,7 +14491,7 @@
         <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>101</v>
@@ -14502,7 +14506,7 @@
         <v>78</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>78</v>
@@ -14513,10 +14517,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14631,10 +14635,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14751,10 +14755,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14780,10 +14784,10 @@
         <v>109</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14795,7 +14799,7 @@
         <v>78</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>78</v>
@@ -14810,13 +14814,13 @@
         <v>78</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>78</v>
@@ -14834,7 +14838,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14843,25 +14847,25 @@
         <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>78</v>
@@ -14869,10 +14873,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14898,16 +14902,16 @@
         <v>176</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -14956,7 +14960,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14971,19 +14975,19 @@
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>78</v>
@@ -14991,10 +14995,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15020,16 +15024,16 @@
         <v>109</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -15054,13 +15058,13 @@
         <v>78</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>78</v>
@@ -15078,7 +15082,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15099,13 +15103,13 @@
         <v>78</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>78</v>
@@ -15113,10 +15117,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15139,16 +15143,16 @@
         <v>90</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15198,7 +15202,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15233,10 +15237,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15262,10 +15266,10 @@
         <v>232</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15316,7 +15320,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15340,10 +15344,10 @@
         <v>132</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>78</v>
@@ -15351,13 +15355,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>78</v>
@@ -15379,17 +15383,17 @@
         <v>90</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -15438,7 +15442,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15447,7 +15451,7 @@
         <v>80</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>101</v>
@@ -15462,7 +15466,7 @@
         <v>78</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>78</v>
@@ -15473,10 +15477,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15591,10 +15595,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15711,10 +15715,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15740,10 +15744,10 @@
         <v>109</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15755,7 +15759,7 @@
         <v>78</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>78</v>
@@ -15770,13 +15774,13 @@
         <v>78</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>78</v>
@@ -15794,7 +15798,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15803,25 +15807,25 @@
         <v>89</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>78</v>
@@ -15829,10 +15833,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15858,16 +15862,16 @@
         <v>176</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>78</v>
@@ -15916,7 +15920,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -15931,19 +15935,19 @@
         <v>101</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>78</v>
@@ -15951,10 +15955,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15980,16 +15984,16 @@
         <v>109</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -16014,13 +16018,13 @@
         <v>78</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>78</v>
@@ -16038,7 +16042,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16059,13 +16063,13 @@
         <v>78</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>78</v>
@@ -16073,10 +16077,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16099,16 +16103,16 @@
         <v>90</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16158,7 +16162,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16193,10 +16197,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16222,10 +16226,10 @@
         <v>232</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16276,7 +16280,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16300,10 +16304,10 @@
         <v>132</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP118" t="s" s="2">
         <v>78</v>
@@ -16311,13 +16315,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>78</v>
@@ -16339,17 +16343,17 @@
         <v>90</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>78</v>
@@ -16398,7 +16402,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16407,7 +16411,7 @@
         <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>101</v>
@@ -16422,7 +16426,7 @@
         <v>78</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>78</v>
@@ -16433,10 +16437,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16551,10 +16555,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16671,10 +16675,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16700,10 +16704,10 @@
         <v>109</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16715,7 +16719,7 @@
         <v>78</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>78</v>
@@ -16730,13 +16734,13 @@
         <v>78</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>78</v>
@@ -16754,7 +16758,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16763,25 +16767,25 @@
         <v>89</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>78</v>
@@ -16789,10 +16793,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16818,16 +16822,16 @@
         <v>176</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16876,7 +16880,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16891,19 +16895,19 @@
         <v>101</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>78</v>
@@ -16911,10 +16915,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16940,16 +16944,16 @@
         <v>109</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -16974,13 +16978,13 @@
         <v>78</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>78</v>
@@ -16998,7 +17002,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17019,13 +17023,13 @@
         <v>78</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>78</v>
@@ -17033,10 +17037,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17059,16 +17063,16 @@
         <v>90</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17118,7 +17122,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17153,10 +17157,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17182,10 +17186,10 @@
         <v>232</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17236,7 +17240,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17260,10 +17264,10 @@
         <v>132</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP126" t="s" s="2">
         <v>78</v>
@@ -17271,10 +17275,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17297,16 +17301,16 @@
         <v>78</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17356,7 +17360,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17380,7 +17384,7 @@
         <v>78</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>78</v>
@@ -17391,10 +17395,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17509,10 +17513,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17629,14 +17633,14 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -17658,10 +17662,10 @@
         <v>134</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>182</v>
@@ -17716,7 +17720,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17751,10 +17755,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17780,10 +17784,10 @@
         <v>109</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17810,13 +17814,13 @@
         <v>78</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>78</v>
@@ -17834,7 +17838,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17858,7 +17862,7 @@
         <v>78</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>78</v>
@@ -17869,10 +17873,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17898,10 +17902,10 @@
         <v>219</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17952,7 +17956,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -17976,7 +17980,7 @@
         <v>78</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>78</v>
@@ -17987,10 +17991,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18013,16 +18017,16 @@
         <v>78</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18072,7 +18076,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18096,7 +18100,7 @@
         <v>78</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>78</v>
@@ -18107,10 +18111,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18133,16 +18137,16 @@
         <v>78</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18192,7 +18196,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18216,7 +18220,7 @@
         <v>78</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>78</v>
@@ -18227,10 +18231,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18253,13 +18257,13 @@
         <v>78</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18310,7 +18314,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18334,7 +18338,7 @@
         <v>78</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>78</v>
@@ -18345,10 +18349,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18463,10 +18467,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18583,14 +18587,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -18612,10 +18616,10 @@
         <v>134</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>182</v>
@@ -18670,7 +18674,7 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -18705,10 +18709,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18734,10 +18738,10 @@
         <v>176</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -18788,7 +18792,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>89</v>
@@ -18823,10 +18827,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18852,10 +18856,10 @@
         <v>232</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18906,7 +18910,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18930,7 +18934,7 @@
         <v>78</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>78</v>
@@ -18941,10 +18945,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18970,10 +18974,10 @@
         <v>176</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19024,7 +19028,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19048,7 +19052,7 @@
         <v>78</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>78</v>
@@ -19059,10 +19063,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19085,17 +19089,17 @@
         <v>78</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
@@ -19144,7 +19148,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19153,13 +19157,13 @@
         <v>80</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -639,7 +639,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>418: source value from NEW PERSON - TITLE &gt; TITLE - NAME (200-8 &gt; 3.1-.01)</t>
+    <t>418: source value based on NEW PERSON - TITLE &gt; TITLE - NAME (200-8 &gt; 3.1-.01)</t>
   </si>
   <si>
     <t>SStaff.SStaff.PositionTitle,Staff.Staff.PositionTitle</t>
@@ -718,10 +718,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-pr-16-411:200-8932.1 &gt; 200.05-3: if date &gt; now or = null then true {null}pr-16-412:200-8932.1 &gt; 200.05-3: if date &lt; now then false {null}</t>
-  </si>
-  <si>
-    <t>412: fixed value = false when NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Expiration Date (200-8932.1 &gt; 200.05-3) case date &lt; now</t>
+pr-16-411:If (200-8932.1 &gt; 200.05-3) is date &gt; now or = null then fixed value true {null}pr-16-412:If (200-8932.1 &gt; 200.05-3) is date &lt; now then fixed value false {null}</t>
+  </si>
+  <si>
+    <t>412: fixed value = false when NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Expiration Date (200-8932.1 &gt; 200.05-3) if date &lt; now</t>
   </si>
   <si>
     <t>StaffSub.ProviderTypeAssignment.ExpirationDateTime</t>
@@ -793,7 +793,7 @@
 </t>
   </si>
   <si>
-    <t>413: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Effective Date (200-8932.1 &gt; 200.05-2)</t>
+    <t>413: source value based on NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Effective Date (200-8932.1 &gt; 200.05-2)</t>
   </si>
   <si>
     <t>StaffSub.ProviderTypeAssignment.EffectiveDateTime</t>
@@ -823,7 +823,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>416: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Expiration Date (200-8932.1 &gt; 200.05-3)</t>
+    <t>416: source value based on NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Expiration Date (200-8932.1 &gt; 200.05-3)</t>
   </si>
   <si>
     <t>DR.2</t>
@@ -849,7 +849,7 @@
 </t>
   </si>
   <si>
-    <t>414: reference from NEW PERSON - NAME (200-.01)</t>
+    <t>414: reference based on NEW PERSON - NAME (200-.01)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.StaffName,SStaff.SStaff.StaffName</t>
@@ -871,7 +871,7 @@
     <t>The organization where the Practitioner performs the roles associated.</t>
   </si>
   <si>
-    <t>1411: reference from NEW PERSON - DIVISION (200-16)</t>
+    <t>1411: reference based on NEW PERSON - DIVISION (200-16)</t>
   </si>
   <si>
     <t>.scoper</t>
@@ -988,7 +988,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1408: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Person Class &gt; PERSON CLASS - X12 CODE (200-8932.1 &gt; 200.05-.01 &gt; 8932.1-6)</t>
+    <t>1408: source value based on NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Person Class &gt; PERSON CLASS - X12 CODE (200-8932.1 &gt; 200.05-.01 &gt; 8932.1-6)</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1012,7 +1012,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1408-2: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Person Class &gt; PERSON CLASS - CLASSIFICATION (200-8932.1 &gt; 200.05-.01 &gt; 8932.1-1)</t>
+    <t>1408-2: source value based on NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Person Class &gt; PERSON CLASS - CLASSIFICATION (200-8932.1 &gt; 200.05-.01 &gt; 8932.1-1)</t>
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
@@ -1096,7 +1096,7 @@
     <t>PractitionerRole.specialty.coding.code</t>
   </si>
   <si>
-    <t>419: source value from NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Person Class &gt; PERSON CLASS - X12 CODE (200-8932.1 &gt; 200.05-.01 &gt; 8932.1-6)</t>
+    <t>419: source value based on NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Person Class &gt; PERSON CLASS - X12 CODE (200-8932.1 &gt; 200.05-.01 &gt; 8932.1-6)</t>
   </si>
   <si>
     <t>PractitionerRole.specialty.coding.display</t>
@@ -1128,10 +1128,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-pr-16-422:44-: if 44-2600&gt;44.1-.01&gt;200 then /Location {null}</t>
-  </si>
-  <si>
-    <t>422: reference from HOSPITAL LOCATION - (44-) case 44-2600&gt;44.1-.01&gt;200</t>
+pr-16-422:If 44-2600&gt;44.1-.01&gt;200 then reference /Location based on (44-) {null}</t>
+  </si>
+  <si>
+    <t>422: reference based on HOSPITAL LOCATION - (44-) if 44-2600&gt;44.1-.01&gt;200</t>
   </si>
   <si>
     <t>.performance.ActDefinitionOrEvent.ServiceDeliveryLocation[@classCode = 'SDLOC']</t>
@@ -1350,7 +1350,7 @@
     <t>PractitionerRole.telecom:va-work.value</t>
   </si>
   <si>
-    <t>384: source value from NEW PERSON - OFFICE PHONE (200-.132)</t>
+    <t>384: source value based on NEW PERSON - OFFICE PHONE (200-.132)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.OfficePhone,SStaff.SStaff.OfficePhone</t>
@@ -1392,7 +1392,7 @@
     <t>PractitionerRole.telecom:va-phone3.value</t>
   </si>
   <si>
-    <t>385: source value from NEW PERSON - PHONE #3 (200-.133)</t>
+    <t>385: source value based on NEW PERSON - PHONE #3 (200-.133)</t>
   </si>
   <si>
     <t>SStaff.SStaff.Phone3</t>
@@ -1428,7 +1428,7 @@
     <t>PractitionerRole.telecom:va-phone4.value</t>
   </si>
   <si>
-    <t>386: source value from NEW PERSON - PHONE #4 (200-.134)</t>
+    <t>386: source value based on NEW PERSON - PHONE #4 (200-.134)</t>
   </si>
   <si>
     <t>SStaff.SStaff.Phone4</t>
@@ -1464,7 +1464,7 @@
     <t>PractitionerRole.telecom:va-commercial.value</t>
   </si>
   <si>
-    <t>387: source value from NEW PERSON - COMMERCIAL PHONE (200-.135)</t>
+    <t>387: source value based on NEW PERSON - COMMERCIAL PHONE (200-.135)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.CommercialPhone,SStaff.SStaff.CommercialPhone</t>
@@ -1506,7 +1506,7 @@
     <t>PractitionerRole.telecom:va-fax.value</t>
   </si>
   <si>
-    <t>388: source value from NEW PERSON - FAX NUMBER (200-.136)</t>
+    <t>388: source value based on NEW PERSON - FAX NUMBER (200-.136)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.FaxNumber,SStaff.SStaff.FaxNumber</t>
@@ -1548,7 +1548,7 @@
     <t>PractitionerRole.telecom:va-voice-pager.value</t>
   </si>
   <si>
-    <t>389: source value from NEW PERSON - VOICE PAGER (200-.137)</t>
+    <t>389: source value based on NEW PERSON - VOICE PAGER (200-.137)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.VoicePager,SStaff.SStaff.VoicePager</t>
@@ -1584,7 +1584,7 @@
     <t>PractitionerRole.telecom:va-data-pager.value</t>
   </si>
   <si>
-    <t>390: source value from NEW PERSON - DIGITAL PAGER (200-.138)</t>
+    <t>390: source value based on NEW PERSON - DIGITAL PAGER (200-.138)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.DigitalPager,SStaff.SStaff.DigitalPager</t>
@@ -1623,7 +1623,7 @@
     <t>PractitionerRole.telecom:va-mail.value</t>
   </si>
   <si>
-    <t>391: source value from NEW PERSON - EMAIL ADDRESS (200-.151)</t>
+    <t>391: source value based on NEW PERSON - EMAIL ADDRESS (200-.151)</t>
   </si>
   <si>
     <t>SStaff.PrescribingProvider.EmailAddress,SStaff.SStaff.EmailAddress</t>
@@ -2147,7 +2147,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="154.08984375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="158.18359375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="71.54296875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="85.47265625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="78.58203125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -718,7 +718,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-pr-16-411:If (200-8932.1 &gt; 200.05-3) is date &gt; now or = null then fixed value true {null}pr-16-412:If (200-8932.1 &gt; 200.05-3) is date &lt; now then fixed value false {null}</t>
+pr-16-411:If (200-8932.1 &gt; 200.05-3) is date &gt; now or = null then fixed value true {true}pr-16-412:If (200-8932.1 &gt; 200.05-3) is date &lt; now then fixed value false {true}</t>
   </si>
   <si>
     <t>412: fixed value = false when NEW PERSON - PERSON CLASS &gt; PERSON CLASS - Expiration Date (200-8932.1 &gt; 200.05-3) if date &lt; now</t>
@@ -1128,7 +1128,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-pr-16-422:If 44-2600&gt;44.1-.01&gt;200 then reference /Location based on (44-) {null}</t>
+pr-16-422:If 44-2600&gt;44.1-.01&gt;200 then reference /Location based on (44-) {true}</t>
   </si>
   <si>
     <t>422: reference based on HOSPITAL LOCATION - (44-) if 44-2600&gt;44.1-.01&gt;200</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PractitionerRole.xlsx
+++ b/docs/StructureDefinition-PractitionerRole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
